--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128586544</v>
+        <v>128589328</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>80189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447634</v>
+        <v>447558</v>
       </c>
       <c r="R2" t="n">
-        <v>7022247</v>
+        <v>7022168</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128589328</v>
+        <v>128586544</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>91452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447558</v>
+        <v>447634</v>
       </c>
       <c r="R3" t="n">
-        <v>7022168</v>
+        <v>7022247</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128587013</v>
+        <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>75162</v>
+        <v>91810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447663</v>
+        <v>447664</v>
       </c>
       <c r="R7" t="n">
-        <v>7022106</v>
+        <v>7022270</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,6 +1316,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1337,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128587720</v>
+        <v>128587013</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>75162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447673</v>
+        <v>447663</v>
       </c>
       <c r="R8" t="n">
-        <v>7022084</v>
+        <v>7022106</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128586050</v>
+        <v>128587720</v>
       </c>
       <c r="B9" t="n">
-        <v>91810</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447664</v>
+        <v>447673</v>
       </c>
       <c r="R9" t="n">
-        <v>7022270</v>
+        <v>7022084</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,21 +1550,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1673,57 +1673,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128588025</v>
+        <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>80216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447724</v>
+        <v>447602</v>
       </c>
       <c r="R11" t="n">
-        <v>7022011</v>
+        <v>7022100</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,48 +1780,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128588534</v>
+        <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>80216</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447602</v>
+        <v>447724</v>
       </c>
       <c r="R12" t="n">
-        <v>7022100</v>
+        <v>7022011</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>92387</v>
+        <v>91748</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R13" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>91748</v>
+        <v>92387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R14" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,38 +2110,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128591182</v>
+        <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>91452</v>
+        <v>79242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2150,13 +2154,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447727</v>
+        <v>447666</v>
       </c>
       <c r="R15" t="n">
-        <v>7022210</v>
+        <v>7022106</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2185,7 +2189,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,7 +2199,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,42 +2226,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128586927</v>
+        <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>79242</v>
+        <v>91452</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447666</v>
+        <v>447727</v>
       </c>
       <c r="R16" t="n">
-        <v>7022106</v>
+        <v>7022210</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586645</v>
+        <v>128588406</v>
       </c>
       <c r="B19" t="n">
-        <v>91452</v>
+        <v>75171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,42 +2568,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447644</v>
+        <v>447602</v>
       </c>
       <c r="R19" t="n">
-        <v>7022249</v>
+        <v>7022100</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,48 +2664,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586291</v>
+        <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>75162</v>
+        <v>91452</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447651</v>
+        <v>447644</v>
       </c>
       <c r="R20" t="n">
-        <v>7022237</v>
+        <v>7022249</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B21" t="n">
-        <v>75171</v>
+        <v>75162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R21" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3107,42 +3107,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128587320</v>
+        <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>79271</v>
+        <v>91452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230552</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,13 +3147,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447668</v>
+        <v>447525</v>
       </c>
       <c r="R24" t="n">
-        <v>7022109</v>
+        <v>7022147</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3186,7 +3182,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,7 +3192,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,38 +3219,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128589039</v>
+        <v>128587320</v>
       </c>
       <c r="B25" t="n">
-        <v>91452</v>
+        <v>79271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>230552</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447525</v>
+        <v>447668</v>
       </c>
       <c r="R25" t="n">
-        <v>7022147</v>
+        <v>7022109</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128586443</v>
+        <v>128587720</v>
       </c>
       <c r="B6" t="n">
-        <v>100753</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447624</v>
+        <v>447673</v>
       </c>
       <c r="R6" t="n">
-        <v>7022238</v>
+        <v>7022084</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128587720</v>
+        <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>100753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447673</v>
+        <v>447624</v>
       </c>
       <c r="R9" t="n">
-        <v>7022084</v>
+        <v>7022238</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3335,32 +3335,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128586312</v>
+        <v>128589765</v>
       </c>
       <c r="B26" t="n">
-        <v>91452</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447610</v>
+        <v>447553</v>
       </c>
       <c r="R26" t="n">
-        <v>7022251</v>
+        <v>7022148</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,7 +3442,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B27" t="n">
         <v>98571</v>
@@ -3470,20 +3470,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R27" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3521,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3531,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3549,57 +3558,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128591228</v>
+        <v>128586312</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>91452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447721</v>
+        <v>447610</v>
       </c>
       <c r="R28" t="n">
-        <v>7022210</v>
+        <v>7022251</v>
       </c>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128589328</v>
+        <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>91458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447558</v>
+        <v>447634</v>
       </c>
       <c r="R2" t="n">
-        <v>7022168</v>
+        <v>7022247</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128586544</v>
+        <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>91452</v>
+        <v>80193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447634</v>
+        <v>447558</v>
       </c>
       <c r="R3" t="n">
-        <v>7022247</v>
+        <v>7022168</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128590184</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587720</v>
+        <v>128587013</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>75166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447673</v>
+        <v>447663</v>
       </c>
       <c r="R6" t="n">
-        <v>7022084</v>
+        <v>7022106</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128586050</v>
+        <v>128587720</v>
       </c>
       <c r="B7" t="n">
-        <v>91810</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447664</v>
+        <v>447673</v>
       </c>
       <c r="R7" t="n">
-        <v>7022270</v>
+        <v>7022084</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,21 +1321,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1347,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128587013</v>
+        <v>128586443</v>
       </c>
       <c r="B8" t="n">
-        <v>75162</v>
+        <v>100761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>492</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447663</v>
+        <v>447624</v>
       </c>
       <c r="R8" t="n">
-        <v>7022106</v>
+        <v>7022238</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128586443</v>
+        <v>128586050</v>
       </c>
       <c r="B9" t="n">
-        <v>100753</v>
+        <v>91816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,13 +1479,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447624</v>
+        <v>447664</v>
       </c>
       <c r="R9" t="n">
-        <v>7022238</v>
+        <v>7022270</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,6 +1535,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,48 +1673,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128588534</v>
+        <v>128588025</v>
       </c>
       <c r="B11" t="n">
-        <v>80216</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447602</v>
+        <v>447724</v>
       </c>
       <c r="R11" t="n">
-        <v>7022100</v>
+        <v>7022011</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,57 +1789,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128588025</v>
+        <v>128588534</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>80220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447724</v>
+        <v>447602</v>
       </c>
       <c r="R12" t="n">
-        <v>7022011</v>
+        <v>7022100</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,7 +1899,7 @@
         <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>91748</v>
+        <v>91754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128587761</v>
       </c>
       <c r="B17" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128591149</v>
       </c>
       <c r="B18" t="n">
-        <v>78060</v>
+        <v>78064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,32 +2557,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B19" t="n">
-        <v>75171</v>
+        <v>75166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R19" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,7 +2667,7 @@
         <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128586291</v>
+        <v>128588406</v>
       </c>
       <c r="B21" t="n">
-        <v>75162</v>
+        <v>75175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447651</v>
+        <v>447602</v>
       </c>
       <c r="R21" t="n">
-        <v>7022237</v>
+        <v>7022100</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128589408</v>
       </c>
       <c r="B23" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128587320</v>
       </c>
       <c r="B25" t="n">
-        <v>79271</v>
+        <v>79275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3335,32 +3335,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589765</v>
+        <v>128586312</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>91458</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447553</v>
+        <v>447610</v>
       </c>
       <c r="R26" t="n">
-        <v>7022148</v>
+        <v>7022251</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3445,7 +3445,7 @@
         <v>128591228</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3558,32 +3558,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128586312</v>
+        <v>128589765</v>
       </c>
       <c r="B28" t="n">
-        <v>91452</v>
+        <v>98579</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3593,13 +3593,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447610</v>
+        <v>447553</v>
       </c>
       <c r="R28" t="n">
-        <v>7022251</v>
+        <v>7022148</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128586544</v>
+        <v>128589328</v>
       </c>
       <c r="B2" t="n">
-        <v>91458</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447634</v>
+        <v>447558</v>
       </c>
       <c r="R2" t="n">
-        <v>7022247</v>
+        <v>7022168</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128589328</v>
+        <v>128586544</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>91464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447558</v>
+        <v>447634</v>
       </c>
       <c r="R3" t="n">
-        <v>7022168</v>
+        <v>7022247</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1230,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128587720</v>
+        <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>91822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447673</v>
+        <v>447664</v>
       </c>
       <c r="R7" t="n">
-        <v>7022084</v>
+        <v>7022270</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,6 +1321,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1337,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128586443</v>
+        <v>128587720</v>
       </c>
       <c r="B8" t="n">
-        <v>100761</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447624</v>
+        <v>447673</v>
       </c>
       <c r="R8" t="n">
-        <v>7022238</v>
+        <v>7022084</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128586050</v>
+        <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>91816</v>
+        <v>100768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447664</v>
+        <v>447624</v>
       </c>
       <c r="R9" t="n">
-        <v>7022270</v>
+        <v>7022238</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,21 +1550,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B13" t="n">
-        <v>91754</v>
+        <v>92399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R13" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B14" t="n">
-        <v>92393</v>
+        <v>91760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R14" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128587761</v>
       </c>
       <c r="B17" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,32 +2557,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586291</v>
+        <v>128588406</v>
       </c>
       <c r="B19" t="n">
-        <v>75166</v>
+        <v>75175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447651</v>
+        <v>447602</v>
       </c>
       <c r="R19" t="n">
-        <v>7022237</v>
+        <v>7022100</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,7 +2667,7 @@
         <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B21" t="n">
-        <v>75175</v>
+        <v>75166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R21" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,32 +3335,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128586312</v>
+        <v>128589765</v>
       </c>
       <c r="B26" t="n">
-        <v>91458</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447610</v>
+        <v>447553</v>
       </c>
       <c r="R26" t="n">
-        <v>7022251</v>
+        <v>7022148</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3445,7 +3445,7 @@
         <v>128591228</v>
       </c>
       <c r="B27" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3558,32 +3558,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128589765</v>
+        <v>128586312</v>
       </c>
       <c r="B28" t="n">
-        <v>98579</v>
+        <v>91464</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3593,13 +3593,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447553</v>
+        <v>447610</v>
       </c>
       <c r="R28" t="n">
-        <v>7022148</v>
+        <v>7022251</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1673,57 +1673,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128588025</v>
+        <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>80220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447724</v>
+        <v>447602</v>
       </c>
       <c r="R11" t="n">
-        <v>7022011</v>
+        <v>7022100</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,48 +1780,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128588534</v>
+        <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>80220</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447602</v>
+        <v>447724</v>
       </c>
       <c r="R12" t="n">
-        <v>7022100</v>
+        <v>7022011</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3219,10 +3219,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128587320</v>
+        <v>128589765</v>
       </c>
       <c r="B25" t="n">
-        <v>79275</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,46 +3230,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230552</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447668</v>
+        <v>447553</v>
       </c>
       <c r="R25" t="n">
-        <v>7022109</v>
+        <v>7022148</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,7 +3326,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B26" t="n">
         <v>98585</v>
@@ -3363,20 +3354,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R26" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,57 +3442,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591228</v>
+        <v>128586312</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>91464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447721</v>
+        <v>447610</v>
       </c>
       <c r="R27" t="n">
-        <v>7022210</v>
+        <v>7022251</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3521,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3531,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,113 +3546,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>128586312</v>
-      </c>
-      <c r="B28" t="n">
-        <v>91464</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>447610</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7022251</v>
-      </c>
-      <c r="S28" t="n">
-        <v>11</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Mattmar</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128589328</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128586544</v>
       </c>
       <c r="B3" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128590184</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587013</v>
+        <v>128587720</v>
       </c>
       <c r="B6" t="n">
-        <v>75166</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447663</v>
+        <v>447673</v>
       </c>
       <c r="R6" t="n">
-        <v>7022106</v>
+        <v>7022084</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128586050</v>
+        <v>128587013</v>
       </c>
       <c r="B7" t="n">
-        <v>91822</v>
+        <v>75168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447664</v>
+        <v>447663</v>
       </c>
       <c r="R7" t="n">
-        <v>7022270</v>
+        <v>7022106</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,21 +1321,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128587720</v>
+        <v>128586050</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>91824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447673</v>
+        <v>447664</v>
       </c>
       <c r="R8" t="n">
-        <v>7022084</v>
+        <v>7022270</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,6 +1428,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1462,7 +1462,7 @@
         <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>80220</v>
+        <v>80222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>92399</v>
+        <v>91762</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R13" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>91760</v>
+        <v>92401</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R14" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,7 +2113,7 @@
         <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B17" t="n">
-        <v>91464</v>
+        <v>78066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,42 +2349,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R17" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B18" t="n">
-        <v>78064</v>
+        <v>91466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,37 +2456,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R18" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128588406</v>
+        <v>128586645</v>
       </c>
       <c r="B19" t="n">
-        <v>75175</v>
+        <v>91466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,37 +2568,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447602</v>
+        <v>447644</v>
       </c>
       <c r="R19" t="n">
-        <v>7022100</v>
+        <v>7022249</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,53 +2669,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586645</v>
+        <v>128586291</v>
       </c>
       <c r="B20" t="n">
-        <v>91464</v>
+        <v>75168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447644</v>
+        <v>447651</v>
       </c>
       <c r="R20" t="n">
-        <v>7022249</v>
+        <v>7022237</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128586291</v>
+        <v>128588406</v>
       </c>
       <c r="B21" t="n">
-        <v>75166</v>
+        <v>75177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447651</v>
+        <v>447602</v>
       </c>
       <c r="R21" t="n">
-        <v>7022237</v>
+        <v>7022100</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128589408</v>
       </c>
       <c r="B23" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128589765</v>
+        <v>128586312</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>91466</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447553</v>
+        <v>447610</v>
       </c>
       <c r="R25" t="n">
-        <v>7022148</v>
+        <v>7022251</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3329,7 +3329,7 @@
         <v>128591228</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,32 +3442,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128586312</v>
+        <v>128589765</v>
       </c>
       <c r="B27" t="n">
-        <v>91464</v>
+        <v>98588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447610</v>
+        <v>447553</v>
       </c>
       <c r="R27" t="n">
-        <v>7022251</v>
+        <v>7022148</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128589328</v>
+        <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>80195</v>
+        <v>91466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447558</v>
+        <v>447634</v>
       </c>
       <c r="R2" t="n">
-        <v>7022168</v>
+        <v>7022247</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128586544</v>
+        <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>80195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447634</v>
+        <v>447558</v>
       </c>
       <c r="R3" t="n">
-        <v>7022247</v>
+        <v>7022168</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587720</v>
+        <v>128587013</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>75168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447673</v>
+        <v>447663</v>
       </c>
       <c r="R6" t="n">
-        <v>7022084</v>
+        <v>7022106</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128587013</v>
+        <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>75168</v>
+        <v>91824</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447663</v>
+        <v>447664</v>
       </c>
       <c r="R7" t="n">
-        <v>7022106</v>
+        <v>7022270</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,6 +1321,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1337,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128586050</v>
+        <v>128587720</v>
       </c>
       <c r="B8" t="n">
-        <v>91824</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447664</v>
+        <v>447673</v>
       </c>
       <c r="R8" t="n">
-        <v>7022270</v>
+        <v>7022084</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,21 +1443,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1462,7 +1462,7 @@
         <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586645</v>
+        <v>128588406</v>
       </c>
       <c r="B19" t="n">
-        <v>91466</v>
+        <v>75177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,42 +2568,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447644</v>
+        <v>447602</v>
       </c>
       <c r="R19" t="n">
-        <v>7022249</v>
+        <v>7022100</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,48 +2664,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586291</v>
+        <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>75168</v>
+        <v>91466</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447651</v>
+        <v>447644</v>
       </c>
       <c r="R20" t="n">
-        <v>7022237</v>
+        <v>7022249</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B21" t="n">
-        <v>75177</v>
+        <v>75168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R21" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3219,48 +3219,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128586312</v>
+        <v>128591228</v>
       </c>
       <c r="B25" t="n">
-        <v>91466</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447610</v>
+        <v>447721</v>
       </c>
       <c r="R25" t="n">
-        <v>7022251</v>
+        <v>7022210</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3289,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3326,10 +3335,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591228</v>
+        <v>128589765</v>
       </c>
       <c r="B26" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,29 +3363,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447721</v>
+        <v>447553</v>
       </c>
       <c r="R26" t="n">
-        <v>7022210</v>
+        <v>7022148</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,32 +3442,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128589765</v>
+        <v>128586312</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>91466</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447553</v>
+        <v>447610</v>
       </c>
       <c r="R27" t="n">
-        <v>7022148</v>
+        <v>7022251</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128588406</v>
+        <v>128586645</v>
       </c>
       <c r="B19" t="n">
-        <v>75177</v>
+        <v>91466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,37 +2568,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447602</v>
+        <v>447644</v>
       </c>
       <c r="R19" t="n">
-        <v>7022100</v>
+        <v>7022249</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,53 +2669,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586645</v>
+        <v>128586291</v>
       </c>
       <c r="B20" t="n">
-        <v>91466</v>
+        <v>75168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447644</v>
+        <v>447651</v>
       </c>
       <c r="R20" t="n">
-        <v>7022249</v>
+        <v>7022237</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128586291</v>
+        <v>128588406</v>
       </c>
       <c r="B21" t="n">
-        <v>75168</v>
+        <v>75177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447651</v>
+        <v>447602</v>
       </c>
       <c r="R21" t="n">
-        <v>7022237</v>
+        <v>7022100</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3219,57 +3219,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591228</v>
+        <v>128586312</v>
       </c>
       <c r="B25" t="n">
-        <v>98591</v>
+        <v>91466</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447721</v>
+        <v>447610</v>
       </c>
       <c r="R25" t="n">
-        <v>7022210</v>
+        <v>7022251</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,7 +3326,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B26" t="n">
         <v>98591</v>
@@ -3363,20 +3354,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R26" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,32 +3442,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128586312</v>
+        <v>128589765</v>
       </c>
       <c r="B27" t="n">
-        <v>91466</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447610</v>
+        <v>447553</v>
       </c>
       <c r="R27" t="n">
-        <v>7022251</v>
+        <v>7022148</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>128587761</v>
       </c>
       <c r="B18" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>128586645</v>
       </c>
       <c r="B19" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3219,48 +3219,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128586312</v>
+        <v>128591228</v>
       </c>
       <c r="B25" t="n">
-        <v>91466</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447610</v>
+        <v>447721</v>
       </c>
       <c r="R25" t="n">
-        <v>7022251</v>
+        <v>7022210</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3289,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3326,10 +3335,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591228</v>
+        <v>128589765</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,29 +3363,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447721</v>
+        <v>447553</v>
       </c>
       <c r="R26" t="n">
-        <v>7022210</v>
+        <v>7022148</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,32 +3442,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128589765</v>
+        <v>128586312</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>91467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447553</v>
+        <v>447610</v>
       </c>
       <c r="R27" t="n">
-        <v>7022148</v>
+        <v>7022251</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128590184</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128587013</v>
       </c>
       <c r="B6" t="n">
-        <v>75168</v>
+        <v>75195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>91825</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128587720</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>80222</v>
+        <v>80249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128591149</v>
       </c>
       <c r="B17" t="n">
-        <v>78066</v>
+        <v>78093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>128587761</v>
       </c>
       <c r="B18" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,53 +2557,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586645</v>
+        <v>128586291</v>
       </c>
       <c r="B19" t="n">
-        <v>91467</v>
+        <v>75195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447644</v>
+        <v>447651</v>
       </c>
       <c r="R19" t="n">
-        <v>7022249</v>
+        <v>7022237</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,48 +2664,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586291</v>
+        <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>75168</v>
+        <v>91494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447651</v>
+        <v>447644</v>
       </c>
       <c r="R20" t="n">
-        <v>7022237</v>
+        <v>7022249</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2779,7 +2779,7 @@
         <v>128588406</v>
       </c>
       <c r="B21" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128589408</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128591228</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>128589765</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>128586312</v>
       </c>
       <c r="B27" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3547,6 +3547,3510 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128859396</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>447545</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7022169</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128857156</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91790</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>658</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>447528</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7022120</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128856217</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>447498</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7022166</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128858970</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>447671</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7022102</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, 36 plantor</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128854816</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91948</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>447483</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7022158</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128854957</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>447477</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7022152</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128857221</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>447579</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7022145</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128859191</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>447654</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7022117</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128859166</v>
+      </c>
+      <c r="B36" t="n">
+        <v>75189</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>306</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>447658</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7022103</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128854129</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>447467</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7022162</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128859079</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>447676</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7022093</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Emil Nordin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128857410</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>447636</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7022220</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128857152</v>
+      </c>
+      <c r="B40" t="n">
+        <v>95857</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>447555</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7022150</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128859190</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>447632</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7022138</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128859400</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>447545</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7022169</v>
+      </c>
+      <c r="S42" t="n">
+        <v>9</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128857488</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>447669</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7022248</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128856170</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91948</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>447486</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7022172</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128857090</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91790</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>658</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>447519</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7022129</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128857255</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91695</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>48</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>447578</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7022145</v>
+      </c>
+      <c r="S46" t="n">
+        <v>6</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128859234</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>447586</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7022132</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128859156</v>
+      </c>
+      <c r="B48" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>308</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>447663</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7022108</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128857160</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>447528</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7022120</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128859403</v>
+      </c>
+      <c r="B50" t="n">
+        <v>102084</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>22</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skarptandad daggkåpa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alchemilla oxyodonta</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>447541</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7022174</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128857643</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>447746</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7022160</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128855978</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91790</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>658</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>447481</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7022155</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128856768</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>447518</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7022171</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128857503</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80249</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>447676</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7022228</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128857763</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98619</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>447780</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7022116</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128856585</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80181</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>447500</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7022174</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På sälg i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128859089</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>447640</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7022114</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128859390</v>
+      </c>
+      <c r="B58" t="n">
+        <v>103141</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>447564</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7022182</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128590184</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128587013</v>
       </c>
       <c r="B6" t="n">
-        <v>75195</v>
+        <v>75196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128587720</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B13" t="n">
-        <v>91790</v>
+        <v>92434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R13" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B14" t="n">
-        <v>92429</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R14" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,7 +2113,7 @@
         <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B17" t="n">
-        <v>78093</v>
+        <v>91499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,37 +2349,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R17" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B18" t="n">
-        <v>91494</v>
+        <v>78097</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,42 +2461,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R18" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,32 +2557,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586291</v>
+        <v>128588406</v>
       </c>
       <c r="B19" t="n">
-        <v>75195</v>
+        <v>75205</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447651</v>
+        <v>447602</v>
       </c>
       <c r="R19" t="n">
-        <v>7022237</v>
+        <v>7022100</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,7 +2667,7 @@
         <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B21" t="n">
-        <v>75204</v>
+        <v>75196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R21" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128589408</v>
       </c>
       <c r="B23" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3219,57 +3219,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591228</v>
+        <v>128586312</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>91499</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447721</v>
+        <v>447610</v>
       </c>
       <c r="R25" t="n">
-        <v>7022210</v>
+        <v>7022251</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,10 +3326,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,20 +3354,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R26" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,32 +3442,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128586312</v>
+        <v>128589765</v>
       </c>
       <c r="B27" t="n">
-        <v>91494</v>
+        <v>98625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447610</v>
+        <v>447553</v>
       </c>
       <c r="R27" t="n">
-        <v>7022251</v>
+        <v>7022148</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3549,32 +3549,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128859396</v>
+        <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>100807</v>
+        <v>91795</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447545</v>
+        <v>447528</v>
       </c>
       <c r="R28" t="n">
-        <v>7022169</v>
+        <v>7022120</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,7 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,17 +3654,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91790</v>
+        <v>91499</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3667,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R29" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,44 +3761,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128856217</v>
+        <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>91494</v>
+        <v>100813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3803,13 +3808,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447498</v>
+        <v>447545</v>
       </c>
       <c r="R30" t="n">
-        <v>7022166</v>
+        <v>7022169</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,12 +3853,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,12 +3868,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>128857221</v>
       </c>
       <c r="B34" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>128859166</v>
       </c>
       <c r="B36" t="n">
-        <v>75189</v>
+        <v>75190</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>128859079</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95857</v>
+        <v>95863</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>128859190</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B42" t="n">
-        <v>92429</v>
+        <v>91953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R42" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,7 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5223,44 +5228,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128857488</v>
+        <v>128859400</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>92434</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5270,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447669</v>
+        <v>447545</v>
       </c>
       <c r="R43" t="n">
-        <v>7022248</v>
+        <v>7022169</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5315,12 +5320,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5335,44 +5335,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128856170</v>
+        <v>128857488</v>
       </c>
       <c r="B44" t="n">
-        <v>91948</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447486</v>
+        <v>447669</v>
       </c>
       <c r="R44" t="n">
-        <v>7022172</v>
+        <v>7022248</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
         <v>128857090</v>
       </c>
       <c r="B45" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128857255</v>
       </c>
       <c r="B46" t="n">
-        <v>91695</v>
+        <v>91700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>128859234</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>128859156</v>
       </c>
       <c r="B48" t="n">
-        <v>75196</v>
+        <v>75197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>128859403</v>
       </c>
       <c r="B50" t="n">
-        <v>102084</v>
+        <v>102090</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6144,54 +6144,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128857643</v>
+        <v>128855978</v>
       </c>
       <c r="B51" t="n">
-        <v>98619</v>
+        <v>91795</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447746</v>
+        <v>447481</v>
       </c>
       <c r="R51" t="n">
-        <v>7022160</v>
+        <v>7022155</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6223,7 +6214,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6233,12 +6224,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,17 +6249,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128855978</v>
+        <v>128856768</v>
       </c>
       <c r="B52" t="n">
-        <v>91790</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6276,21 +6267,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6300,10 +6291,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447481</v>
+        <v>447518</v>
       </c>
       <c r="R52" t="n">
-        <v>7022155</v>
+        <v>7022171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6335,7 +6326,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6345,12 +6336,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6370,52 +6361,61 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>98625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R53" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6492,7 +6492,7 @@
         <v>128857503</v>
       </c>
       <c r="B54" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6594,61 +6594,52 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128857763</v>
+        <v>128859089</v>
       </c>
       <c r="B55" t="n">
-        <v>98619</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447780</v>
+        <v>447640</v>
       </c>
       <c r="R55" t="n">
-        <v>7022116</v>
+        <v>7022114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6680,7 +6671,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6690,12 +6681,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6725,7 +6716,7 @@
         <v>128856585</v>
       </c>
       <c r="B56" t="n">
-        <v>80181</v>
+        <v>80185</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6834,45 +6825,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>98625</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R57" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6949,7 +6949,7 @@
         <v>128859390</v>
       </c>
       <c r="B58" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587013</v>
+        <v>128586050</v>
       </c>
       <c r="B6" t="n">
-        <v>75196</v>
+        <v>91862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>492</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447663</v>
+        <v>447664</v>
       </c>
       <c r="R6" t="n">
-        <v>7022106</v>
+        <v>7022270</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,6 +1209,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,32 +1240,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128586050</v>
+        <v>128587720</v>
       </c>
       <c r="B7" t="n">
-        <v>91857</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447664</v>
+        <v>447673</v>
       </c>
       <c r="R7" t="n">
-        <v>7022270</v>
+        <v>7022084</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,21 +1331,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128587720</v>
+        <v>128587013</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>75196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447673</v>
+        <v>447663</v>
       </c>
       <c r="R8" t="n">
-        <v>7022084</v>
+        <v>7022106</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1462,7 @@
         <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>92434</v>
+        <v>91800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R13" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>92439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R14" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B17" t="n">
-        <v>91499</v>
+        <v>78097</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,42 +2349,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R17" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B18" t="n">
-        <v>78097</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,37 +2456,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R18" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,53 +2664,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586645</v>
+        <v>128586291</v>
       </c>
       <c r="B20" t="n">
-        <v>91499</v>
+        <v>75196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447644</v>
+        <v>447651</v>
       </c>
       <c r="R20" t="n">
-        <v>7022249</v>
+        <v>7022237</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2734,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2744,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,48 +2771,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128586291</v>
+        <v>128586645</v>
       </c>
       <c r="B21" t="n">
-        <v>75196</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447651</v>
+        <v>447644</v>
       </c>
       <c r="R21" t="n">
-        <v>7022237</v>
+        <v>7022249</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128586312</v>
       </c>
       <c r="B25" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128591228</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>128589765</v>
       </c>
       <c r="B27" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3549,32 +3549,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128857156</v>
+        <v>128859396</v>
       </c>
       <c r="B28" t="n">
-        <v>91795</v>
+        <v>100820</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447528</v>
+        <v>447545</v>
       </c>
       <c r="R28" t="n">
-        <v>7022120</v>
+        <v>7022169</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,17 +3649,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B29" t="n">
-        <v>91499</v>
+        <v>91800</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3667,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R29" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3736,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,44 +3756,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128859396</v>
+        <v>128856217</v>
       </c>
       <c r="B30" t="n">
-        <v>100813</v>
+        <v>91504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3808,13 +3803,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447545</v>
+        <v>447498</v>
       </c>
       <c r="R30" t="n">
-        <v>7022169</v>
+        <v>7022166</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3853,7 +3848,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,12 +3868,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4118,48 +4118,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128854957</v>
+        <v>128859191</v>
       </c>
       <c r="B33" t="n">
-        <v>91499</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447477</v>
+        <v>447654</v>
       </c>
       <c r="R33" t="n">
-        <v>7022152</v>
+        <v>7022117</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4188,7 +4192,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4198,12 +4202,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,22 +4217,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128857221</v>
+        <v>128854957</v>
       </c>
       <c r="B34" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,24 +4258,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447579</v>
+        <v>447477</v>
       </c>
       <c r="R34" t="n">
-        <v>7022145</v>
+        <v>7022152</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,7 +4299,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4315,7 +4309,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,49 +4329,50 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128859191</v>
+        <v>128857221</v>
       </c>
       <c r="B35" t="n">
-        <v>98625</v>
+        <v>91504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447654</v>
+        <v>447579</v>
       </c>
       <c r="R35" t="n">
-        <v>7022117</v>
+        <v>7022145</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,7 +4568,7 @@
         <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95863</v>
+        <v>95870</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>128856170</v>
       </c>
       <c r="B42" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>128859400</v>
       </c>
       <c r="B43" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5459,32 +5459,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128857090</v>
+        <v>128857255</v>
       </c>
       <c r="B45" t="n">
-        <v>91795</v>
+        <v>91705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5494,13 +5494,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447519</v>
+        <v>447578</v>
       </c>
       <c r="R45" t="n">
-        <v>7022129</v>
+        <v>7022145</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5559,39 +5559,39 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128857255</v>
+        <v>128857090</v>
       </c>
       <c r="B46" t="n">
-        <v>91700</v>
+        <v>91800</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5601,13 +5601,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447578</v>
+        <v>447519</v>
       </c>
       <c r="R46" t="n">
-        <v>7022145</v>
+        <v>7022129</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5676,7 +5676,7 @@
         <v>128859234</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>128859403</v>
       </c>
       <c r="B50" t="n">
-        <v>102090</v>
+        <v>102097</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6144,45 +6144,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128855978</v>
+        <v>128857643</v>
       </c>
       <c r="B51" t="n">
-        <v>91795</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447481</v>
+        <v>447746</v>
       </c>
       <c r="R51" t="n">
-        <v>7022155</v>
+        <v>7022160</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6214,7 +6223,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6224,12 +6233,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6249,17 +6258,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128856768</v>
+        <v>128855978</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>91800</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6267,21 +6276,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6291,10 +6300,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447518</v>
+        <v>447481</v>
       </c>
       <c r="R52" t="n">
-        <v>7022171</v>
+        <v>7022155</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6326,7 +6335,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6336,12 +6345,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6361,61 +6370,52 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128857643</v>
+        <v>128856768</v>
       </c>
       <c r="B53" t="n">
-        <v>98625</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447746</v>
+        <v>447518</v>
       </c>
       <c r="R53" t="n">
-        <v>7022160</v>
+        <v>7022171</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6594,52 +6594,61 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R55" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6671,7 +6680,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6681,12 +6690,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6825,54 +6834,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128857763</v>
+        <v>128859089</v>
       </c>
       <c r="B57" t="n">
-        <v>98625</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447780</v>
+        <v>447640</v>
       </c>
       <c r="R57" t="n">
-        <v>7022116</v>
+        <v>7022114</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6949,7 +6949,7 @@
         <v>128859390</v>
       </c>
       <c r="B58" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B13" t="n">
-        <v>91800</v>
+        <v>92439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R13" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B14" t="n">
-        <v>92439</v>
+        <v>91800</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R14" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128588406</v>
+        <v>128586645</v>
       </c>
       <c r="B19" t="n">
-        <v>75205</v>
+        <v>91504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,37 +2568,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447602</v>
+        <v>447644</v>
       </c>
       <c r="R19" t="n">
-        <v>7022100</v>
+        <v>7022249</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,10 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128586645</v>
+        <v>128588406</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>75205</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,42 +2787,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447644</v>
+        <v>447602</v>
       </c>
       <c r="R21" t="n">
-        <v>7022249</v>
+        <v>7022100</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3326,7 +3326,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591228</v>
+        <v>128589765</v>
       </c>
       <c r="B26" t="n">
         <v>98632</v>
@@ -3354,29 +3354,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447721</v>
+        <v>447553</v>
       </c>
       <c r="R26" t="n">
-        <v>7022210</v>
+        <v>7022148</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3396,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3406,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,7 +3433,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B27" t="n">
         <v>98632</v>
@@ -3470,20 +3461,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R27" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3549,32 +3549,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128859396</v>
+        <v>128856217</v>
       </c>
       <c r="B28" t="n">
-        <v>100820</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447545</v>
+        <v>447498</v>
       </c>
       <c r="R28" t="n">
-        <v>7022169</v>
+        <v>7022166</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,7 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3644,7 +3649,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3768,32 +3773,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128856217</v>
+        <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>91504</v>
+        <v>100820</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3803,13 +3808,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447498</v>
+        <v>447545</v>
       </c>
       <c r="R30" t="n">
-        <v>7022166</v>
+        <v>7022169</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,12 +3853,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,12 +3868,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4118,52 +4118,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128859191</v>
+        <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>91504</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447654</v>
+        <v>447477</v>
       </c>
       <c r="R33" t="n">
-        <v>7022117</v>
+        <v>7022152</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4192,7 +4188,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4202,7 +4198,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,19 +4218,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128854957</v>
+        <v>128857221</v>
       </c>
       <c r="B34" t="n">
         <v>91504</v>
@@ -4258,19 +4259,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447477</v>
+        <v>447579</v>
       </c>
       <c r="R34" t="n">
-        <v>7022152</v>
+        <v>7022145</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4299,7 +4305,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4309,12 +4315,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4329,50 +4330,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128857221</v>
+        <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>91504</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447579</v>
+        <v>447654</v>
       </c>
       <c r="R35" t="n">
-        <v>7022145</v>
+        <v>7022117</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B42" t="n">
-        <v>91958</v>
+        <v>92439</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R42" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,12 +5208,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,44 +5223,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B43" t="n">
-        <v>92439</v>
+        <v>91958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5270,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R43" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5305,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,7 +5315,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5335,12 +5335,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5452,17 +5452,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128857255</v>
+        <v>128859234</v>
       </c>
       <c r="B45" t="n">
-        <v>91705</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5470,37 +5470,51 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447578</v>
+        <v>447586</v>
       </c>
       <c r="R45" t="n">
-        <v>7022145</v>
+        <v>7022132</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5529,7 +5543,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5539,7 +5553,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5554,44 +5573,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128857090</v>
+        <v>128857255</v>
       </c>
       <c r="B46" t="n">
-        <v>91800</v>
+        <v>91705</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5601,13 +5620,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447519</v>
+        <v>447578</v>
       </c>
       <c r="R46" t="n">
-        <v>7022129</v>
+        <v>7022145</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5636,7 +5655,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5646,7 +5665,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5666,69 +5685,55 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128859234</v>
+        <v>128857090</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>91800</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447586</v>
+        <v>447519</v>
       </c>
       <c r="R47" t="n">
-        <v>7022132</v>
+        <v>7022129</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5757,7 +5762,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5767,12 +5772,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5787,12 +5787,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5906,38 +5906,47 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>91504</v>
+        <v>102097</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5946,13 +5955,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R49" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5981,7 +5990,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5991,7 +6000,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6006,59 +6020,50 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B50" t="n">
-        <v>102097</v>
+        <v>91504</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6067,13 +6072,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R50" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6102,7 +6107,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6112,12 +6117,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6132,66 +6132,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128857643</v>
+        <v>128855978</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>91800</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447746</v>
+        <v>447481</v>
       </c>
       <c r="R51" t="n">
-        <v>7022160</v>
+        <v>7022155</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6223,7 +6214,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6233,12 +6224,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,17 +6249,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128855978</v>
+        <v>128856768</v>
       </c>
       <c r="B52" t="n">
-        <v>91800</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6276,21 +6267,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6300,10 +6291,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447481</v>
+        <v>447518</v>
       </c>
       <c r="R52" t="n">
-        <v>7022155</v>
+        <v>7022171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6335,7 +6326,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6345,12 +6336,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6370,52 +6361,61 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R53" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>92439</v>
+        <v>91800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R13" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>91800</v>
+        <v>92439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R14" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B17" t="n">
-        <v>78097</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,37 +2349,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R17" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>78097</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,42 +2461,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R18" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586645</v>
+        <v>128588406</v>
       </c>
       <c r="B19" t="n">
-        <v>91504</v>
+        <v>75205</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,42 +2568,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447644</v>
+        <v>447602</v>
       </c>
       <c r="R19" t="n">
-        <v>7022249</v>
+        <v>7022100</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,48 +2664,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586291</v>
+        <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>75196</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447651</v>
+        <v>447644</v>
       </c>
       <c r="R20" t="n">
-        <v>7022237</v>
+        <v>7022249</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B21" t="n">
-        <v>75205</v>
+        <v>75196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R21" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>91800</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R28" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,22 +3649,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91800</v>
+        <v>91504</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R29" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,12 +3761,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4118,48 +4118,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128854957</v>
+        <v>128859191</v>
       </c>
       <c r="B33" t="n">
-        <v>91504</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447477</v>
+        <v>447654</v>
       </c>
       <c r="R33" t="n">
-        <v>7022152</v>
+        <v>7022117</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4188,7 +4192,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4198,12 +4202,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,19 +4217,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128857221</v>
+        <v>128854957</v>
       </c>
       <c r="B34" t="n">
         <v>91504</v>
@@ -4259,24 +4258,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447579</v>
+        <v>447477</v>
       </c>
       <c r="R34" t="n">
-        <v>7022145</v>
+        <v>7022152</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,7 +4299,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4315,7 +4309,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,49 +4329,50 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128859191</v>
+        <v>128857221</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>91504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447654</v>
+        <v>447579</v>
       </c>
       <c r="R35" t="n">
-        <v>7022117</v>
+        <v>7022145</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6144,45 +6144,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128855978</v>
+        <v>128857643</v>
       </c>
       <c r="B51" t="n">
-        <v>91800</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447481</v>
+        <v>447746</v>
       </c>
       <c r="R51" t="n">
-        <v>7022155</v>
+        <v>7022160</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6214,7 +6223,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6224,12 +6233,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6249,7 +6258,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6368,54 +6377,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128857643</v>
+        <v>128855978</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>91800</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447746</v>
+        <v>447481</v>
       </c>
       <c r="R53" t="n">
-        <v>7022160</v>
+        <v>7022155</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6594,61 +6594,52 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128857763</v>
+        <v>128859089</v>
       </c>
       <c r="B55" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447780</v>
+        <v>447640</v>
       </c>
       <c r="R55" t="n">
-        <v>7022116</v>
+        <v>7022114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6680,7 +6671,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6690,12 +6681,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6722,45 +6713,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128856585</v>
+        <v>128857763</v>
       </c>
       <c r="B56" t="n">
-        <v>80185</v>
+        <v>98632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447500</v>
+        <v>447780</v>
       </c>
       <c r="R56" t="n">
-        <v>7022174</v>
+        <v>7022116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6834,32 +6834,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128859089</v>
+        <v>128856585</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>80185</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447640</v>
+        <v>447500</v>
       </c>
       <c r="R57" t="n">
-        <v>7022114</v>
+        <v>7022174</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128590184</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128586050</v>
+        <v>128587013</v>
       </c>
       <c r="B6" t="n">
-        <v>91862</v>
+        <v>75200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>492</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447664</v>
+        <v>447663</v>
       </c>
       <c r="R6" t="n">
-        <v>7022270</v>
+        <v>7022106</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,21 +1214,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1240,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128587720</v>
+        <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>91866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447673</v>
+        <v>447664</v>
       </c>
       <c r="R7" t="n">
-        <v>7022084</v>
+        <v>7022270</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,6 +1321,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1347,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128587013</v>
+        <v>128587720</v>
       </c>
       <c r="B8" t="n">
-        <v>75196</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447663</v>
+        <v>447673</v>
       </c>
       <c r="R8" t="n">
-        <v>7022106</v>
+        <v>7022084</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1462,7 @@
         <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B13" t="n">
-        <v>91800</v>
+        <v>92443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R13" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B14" t="n">
-        <v>92439</v>
+        <v>91804</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R14" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,7 +2113,7 @@
         <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128587761</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128591149</v>
       </c>
       <c r="B18" t="n">
-        <v>78097</v>
+        <v>78101</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,32 +2557,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B19" t="n">
-        <v>75205</v>
+        <v>75200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R19" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,7 +2667,7 @@
         <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128586291</v>
+        <v>128588406</v>
       </c>
       <c r="B21" t="n">
-        <v>75196</v>
+        <v>75209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447651</v>
+        <v>447602</v>
       </c>
       <c r="R21" t="n">
-        <v>7022237</v>
+        <v>7022100</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128589408</v>
       </c>
       <c r="B23" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128586312</v>
       </c>
       <c r="B25" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,20 +3354,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R26" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3396,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3406,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3433,10 +3442,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591228</v>
+        <v>128589765</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,29 +3470,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447721</v>
+        <v>447553</v>
       </c>
       <c r="R27" t="n">
-        <v>7022210</v>
+        <v>7022148</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3552,7 +3552,7 @@
         <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128859191</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>128854957</v>
       </c>
       <c r="B34" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>128857221</v>
       </c>
       <c r="B35" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>128859166</v>
       </c>
       <c r="B36" t="n">
-        <v>75190</v>
+        <v>75194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128854129</v>
+        <v>128859079</v>
       </c>
       <c r="B37" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447467</v>
+        <v>447676</v>
       </c>
       <c r="R37" t="n">
-        <v>7022162</v>
+        <v>7022093</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4645,12 +4645,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4665,22 +4660,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128859079</v>
+        <v>128854129</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>91508</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,21 +4683,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,13 +4707,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447676</v>
+        <v>447467</v>
       </c>
       <c r="R38" t="n">
-        <v>7022093</v>
+        <v>7022162</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4747,7 +4742,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4757,7 +4752,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4772,12 +4772,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4787,7 +4787,7 @@
         <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95870</v>
+        <v>95874</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>128859190</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
         <v>128859400</v>
       </c>
       <c r="B42" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5235,32 +5235,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128856170</v>
+        <v>128857488</v>
       </c>
       <c r="B43" t="n">
-        <v>91958</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447486</v>
+        <v>447669</v>
       </c>
       <c r="R43" t="n">
-        <v>7022172</v>
+        <v>7022248</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,39 +5340,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128857488</v>
+        <v>128856170</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>91962</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447669</v>
+        <v>447486</v>
       </c>
       <c r="R44" t="n">
-        <v>7022248</v>
+        <v>7022172</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5452,69 +5452,55 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128859234</v>
+        <v>128857090</v>
       </c>
       <c r="B45" t="n">
-        <v>98632</v>
+        <v>91804</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447586</v>
+        <v>447519</v>
       </c>
       <c r="R45" t="n">
-        <v>7022132</v>
+        <v>7022129</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5543,7 +5529,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5553,12 +5539,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,12 +5554,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5588,7 +5569,7 @@
         <v>128857255</v>
       </c>
       <c r="B46" t="n">
-        <v>91705</v>
+        <v>91709</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5692,48 +5673,62 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128857090</v>
+        <v>128859234</v>
       </c>
       <c r="B47" t="n">
-        <v>91800</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447519</v>
+        <v>447586</v>
       </c>
       <c r="R47" t="n">
-        <v>7022129</v>
+        <v>7022132</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5762,7 +5757,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5772,7 +5767,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5787,12 +5787,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5802,7 +5802,7 @@
         <v>128859156</v>
       </c>
       <c r="B48" t="n">
-        <v>75197</v>
+        <v>75201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5909,7 +5909,7 @@
         <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>102097</v>
+        <v>102101</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>128857160</v>
       </c>
       <c r="B50" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6144,54 +6144,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128857643</v>
+        <v>128856768</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447746</v>
+        <v>447518</v>
       </c>
       <c r="R51" t="n">
-        <v>7022160</v>
+        <v>7022171</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6223,7 +6214,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6233,12 +6224,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6258,17 +6249,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128856768</v>
+        <v>128855978</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>91804</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6276,21 +6267,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6300,10 +6291,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447518</v>
+        <v>447481</v>
       </c>
       <c r="R52" t="n">
-        <v>7022171</v>
+        <v>7022155</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6335,7 +6326,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6345,12 +6336,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6370,52 +6361,61 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128855978</v>
+        <v>128857643</v>
       </c>
       <c r="B53" t="n">
-        <v>91800</v>
+        <v>98636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447481</v>
+        <v>447746</v>
       </c>
       <c r="R53" t="n">
-        <v>7022155</v>
+        <v>7022160</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6492,7 +6492,7 @@
         <v>128857503</v>
       </c>
       <c r="B54" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6601,45 +6601,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>98636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R55" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6671,7 +6680,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6681,12 +6690,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6713,54 +6722,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B56" t="n">
-        <v>98632</v>
+        <v>80189</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R56" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6827,39 +6827,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B57" t="n">
-        <v>80185</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R57" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6949,7 +6949,7 @@
         <v>128859390</v>
       </c>
       <c r="B58" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128586544</v>
+        <v>128589328</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>80230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447634</v>
+        <v>447558</v>
       </c>
       <c r="R2" t="n">
-        <v>7022247</v>
+        <v>7022168</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128589328</v>
+        <v>128586544</v>
       </c>
       <c r="B3" t="n">
-        <v>80230</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447558</v>
+        <v>447634</v>
       </c>
       <c r="R3" t="n">
-        <v>7022168</v>
+        <v>7022247</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587013</v>
+        <v>128586050</v>
       </c>
       <c r="B6" t="n">
-        <v>75200</v>
+        <v>91866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>492</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447663</v>
+        <v>447664</v>
       </c>
       <c r="R6" t="n">
-        <v>7022106</v>
+        <v>7022270</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,6 +1209,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128586050</v>
+        <v>128587013</v>
       </c>
       <c r="B7" t="n">
-        <v>91866</v>
+        <v>75200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447664</v>
+        <v>447663</v>
       </c>
       <c r="R7" t="n">
-        <v>7022270</v>
+        <v>7022106</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,21 +1336,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>92443</v>
+        <v>91804</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R13" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>91804</v>
+        <v>92443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R14" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2557,48 +2557,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586291</v>
+        <v>128586645</v>
       </c>
       <c r="B19" t="n">
-        <v>75200</v>
+        <v>91508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447651</v>
+        <v>447644</v>
       </c>
       <c r="R19" t="n">
-        <v>7022237</v>
+        <v>7022249</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,53 +2669,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586645</v>
+        <v>128586291</v>
       </c>
       <c r="B20" t="n">
-        <v>91508</v>
+        <v>75200</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447644</v>
+        <v>447651</v>
       </c>
       <c r="R20" t="n">
-        <v>7022249</v>
+        <v>7022237</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4118,52 +4118,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128859191</v>
+        <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447654</v>
+        <v>447477</v>
       </c>
       <c r="R33" t="n">
-        <v>7022117</v>
+        <v>7022152</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4192,7 +4188,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4202,7 +4198,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,19 +4218,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128854957</v>
+        <v>128857221</v>
       </c>
       <c r="B34" t="n">
         <v>91508</v>
@@ -4258,19 +4259,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447477</v>
+        <v>447579</v>
       </c>
       <c r="R34" t="n">
-        <v>7022152</v>
+        <v>7022145</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4299,7 +4305,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4309,12 +4315,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4329,50 +4330,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128857221</v>
+        <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>91508</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447579</v>
+        <v>447654</v>
       </c>
       <c r="R35" t="n">
-        <v>7022145</v>
+        <v>7022117</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5121,39 +5121,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128859400</v>
+        <v>128857488</v>
       </c>
       <c r="B42" t="n">
-        <v>92443</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447545</v>
+        <v>447669</v>
       </c>
       <c r="R42" t="n">
-        <v>7022169</v>
+        <v>7022248</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,7 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5223,7 +5228,7 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5235,32 +5240,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128857488</v>
+        <v>128856170</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>91962</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5270,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447669</v>
+        <v>447486</v>
       </c>
       <c r="R43" t="n">
-        <v>7022248</v>
+        <v>7022172</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5315,12 +5320,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,39 +5345,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B44" t="n">
-        <v>91962</v>
+        <v>92443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,13 +5387,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R44" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5417,7 +5422,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5427,12 +5432,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128857255</v>
+        <v>128859234</v>
       </c>
       <c r="B46" t="n">
-        <v>91709</v>
+        <v>98636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,37 +5577,51 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447578</v>
+        <v>447586</v>
       </c>
       <c r="R46" t="n">
-        <v>7022145</v>
+        <v>7022132</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5636,7 +5650,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5646,7 +5660,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5661,74 +5680,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128859234</v>
+        <v>128859156</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>75201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447586</v>
+        <v>447663</v>
       </c>
       <c r="R47" t="n">
-        <v>7022132</v>
+        <v>7022108</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5757,7 +5762,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5767,12 +5772,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5787,60 +5787,74 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128859156</v>
+        <v>128859403</v>
       </c>
       <c r="B48" t="n">
-        <v>75201</v>
+        <v>102101</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447663</v>
+        <v>447541</v>
       </c>
       <c r="R48" t="n">
-        <v>7022108</v>
+        <v>7022174</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5869,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5879,7 +5893,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5894,59 +5913,50 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>102101</v>
+        <v>91508</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5955,13 +5965,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R49" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5990,7 +6000,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6000,12 +6010,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6020,22 +6025,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128857160</v>
+        <v>128855978</v>
       </c>
       <c r="B50" t="n">
-        <v>91508</v>
+        <v>91804</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6043,42 +6048,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447528</v>
+        <v>447481</v>
       </c>
       <c r="R50" t="n">
-        <v>7022120</v>
+        <v>7022155</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6117,7 +6117,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6132,57 +6137,66 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R51" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6214,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6224,12 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6249,17 +6263,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128855978</v>
+        <v>128856768</v>
       </c>
       <c r="B52" t="n">
-        <v>91804</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6267,21 +6281,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6291,10 +6305,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447481</v>
+        <v>447518</v>
       </c>
       <c r="R52" t="n">
-        <v>7022155</v>
+        <v>7022171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6326,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6336,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6361,61 +6375,52 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128857643</v>
+        <v>128857503</v>
       </c>
       <c r="B53" t="n">
-        <v>98636</v>
+        <v>80257</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447746</v>
+        <v>447676</v>
       </c>
       <c r="R53" t="n">
-        <v>7022160</v>
+        <v>7022228</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6447,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6457,7 +6462,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6482,52 +6487,61 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128857503</v>
+        <v>128857763</v>
       </c>
       <c r="B54" t="n">
-        <v>80257</v>
+        <v>98636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447676</v>
+        <v>447780</v>
       </c>
       <c r="R54" t="n">
-        <v>7022228</v>
+        <v>7022116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6559,7 +6573,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6569,12 +6583,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6601,54 +6615,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B55" t="n">
-        <v>98636</v>
+        <v>80189</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R55" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6680,7 +6685,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6690,12 +6695,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6722,32 +6727,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B56" t="n">
-        <v>80189</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6757,10 +6762,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R56" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6792,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6802,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6834,32 +6839,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128859089</v>
+        <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>103158</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>222002</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6869,10 +6874,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447640</v>
+        <v>447564</v>
       </c>
       <c r="R57" t="n">
-        <v>7022114</v>
+        <v>7022182</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6904,7 +6909,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6914,12 +6919,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6934,122 +6934,15 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>128859390</v>
-      </c>
-      <c r="B58" t="n">
-        <v>103158</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>222002</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Underviol</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Viola mirabilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>447564</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7022182</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Mattmar</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128589328</v>
+        <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>80230</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447558</v>
+        <v>447634</v>
       </c>
       <c r="R2" t="n">
-        <v>7022168</v>
+        <v>7022247</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128586544</v>
+        <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>80230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447634</v>
+        <v>447558</v>
       </c>
       <c r="R3" t="n">
-        <v>7022247</v>
+        <v>7022168</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128586050</v>
+        <v>128587720</v>
       </c>
       <c r="B6" t="n">
-        <v>91866</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447664</v>
+        <v>447673</v>
       </c>
       <c r="R6" t="n">
-        <v>7022270</v>
+        <v>7022084</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,21 +1209,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1352,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128587720</v>
+        <v>128586443</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>100824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447673</v>
+        <v>447624</v>
       </c>
       <c r="R8" t="n">
-        <v>7022084</v>
+        <v>7022238</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128586443</v>
+        <v>128586050</v>
       </c>
       <c r="B9" t="n">
-        <v>100824</v>
+        <v>91866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,13 +1479,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447624</v>
+        <v>447664</v>
       </c>
       <c r="R9" t="n">
-        <v>7022238</v>
+        <v>7022270</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,6 +1535,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1673,48 +1673,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128588534</v>
+        <v>128588025</v>
       </c>
       <c r="B11" t="n">
-        <v>80257</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447602</v>
+        <v>447724</v>
       </c>
       <c r="R11" t="n">
-        <v>7022100</v>
+        <v>7022011</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,57 +1789,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128588025</v>
+        <v>128588534</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>80257</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447724</v>
+        <v>447602</v>
       </c>
       <c r="R12" t="n">
-        <v>7022011</v>
+        <v>7022100</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B17" t="n">
-        <v>91508</v>
+        <v>78101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,42 +2349,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R17" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B18" t="n">
-        <v>78101</v>
+        <v>91508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,37 +2456,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R18" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586645</v>
+        <v>128588406</v>
       </c>
       <c r="B19" t="n">
-        <v>91508</v>
+        <v>75209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,42 +2568,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447644</v>
+        <v>447602</v>
       </c>
       <c r="R19" t="n">
-        <v>7022249</v>
+        <v>7022100</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,48 +2664,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586291</v>
+        <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>75200</v>
+        <v>91508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447651</v>
+        <v>447644</v>
       </c>
       <c r="R20" t="n">
-        <v>7022237</v>
+        <v>7022249</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B21" t="n">
-        <v>75209</v>
+        <v>75200</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R21" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B28" t="n">
-        <v>91804</v>
+        <v>91508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R28" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,22 +3649,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B29" t="n">
-        <v>91508</v>
+        <v>91804</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R29" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,12 +3761,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5799,47 +5799,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B48" t="n">
-        <v>102101</v>
+        <v>91508</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5848,13 +5839,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R48" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5883,7 +5874,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,12 +5884,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,50 +5899,59 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>91508</v>
+        <v>102101</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5965,13 +5960,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R49" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6000,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6010,7 +6005,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6149,54 +6149,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128857643</v>
+        <v>128856768</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447746</v>
+        <v>447518</v>
       </c>
       <c r="R51" t="n">
-        <v>7022160</v>
+        <v>7022171</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6219,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6229,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6263,52 +6254,61 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>98636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R52" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6487,61 +6487,52 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B54" t="n">
-        <v>98636</v>
+        <v>80189</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R54" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6573,7 +6564,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6583,12 +6574,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6615,32 +6606,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B55" t="n">
-        <v>80189</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6650,10 +6641,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R55" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6685,7 +6676,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6695,12 +6686,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6727,45 +6718,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>98636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R56" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128590184</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587720</v>
+        <v>128587013</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>82996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447673</v>
+        <v>447663</v>
       </c>
       <c r="R6" t="n">
-        <v>7022084</v>
+        <v>7022106</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128587013</v>
+        <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>75200</v>
+        <v>91871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447663</v>
+        <v>447664</v>
       </c>
       <c r="R7" t="n">
-        <v>7022106</v>
+        <v>7022270</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,6 +1321,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1337,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128586443</v>
+        <v>128587720</v>
       </c>
       <c r="B8" t="n">
-        <v>100824</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447624</v>
+        <v>447673</v>
       </c>
       <c r="R8" t="n">
-        <v>7022238</v>
+        <v>7022084</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128586050</v>
+        <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>91866</v>
+        <v>100831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447664</v>
+        <v>447624</v>
       </c>
       <c r="R9" t="n">
-        <v>7022270</v>
+        <v>7022238</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,21 +1550,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,57 +1673,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128588025</v>
+        <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>80162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447724</v>
+        <v>447602</v>
       </c>
       <c r="R11" t="n">
-        <v>7022011</v>
+        <v>7022100</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,48 +1780,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128588534</v>
+        <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>80257</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447602</v>
+        <v>447724</v>
       </c>
       <c r="R12" t="n">
-        <v>7022100</v>
+        <v>7022011</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,7 +1899,7 @@
         <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B17" t="n">
-        <v>78101</v>
+        <v>91513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,37 +2349,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R17" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B18" t="n">
-        <v>91508</v>
+        <v>78042</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,42 +2461,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R18" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128588406</v>
+        <v>128586645</v>
       </c>
       <c r="B19" t="n">
-        <v>75209</v>
+        <v>91513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,37 +2568,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447602</v>
+        <v>447644</v>
       </c>
       <c r="R19" t="n">
-        <v>7022100</v>
+        <v>7022249</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,53 +2669,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586645</v>
+        <v>128586291</v>
       </c>
       <c r="B20" t="n">
-        <v>91508</v>
+        <v>82996</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447644</v>
+        <v>447651</v>
       </c>
       <c r="R20" t="n">
-        <v>7022249</v>
+        <v>7022237</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128586291</v>
+        <v>128588406</v>
       </c>
       <c r="B21" t="n">
-        <v>75200</v>
+        <v>83005</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447651</v>
+        <v>447602</v>
       </c>
       <c r="R21" t="n">
-        <v>7022237</v>
+        <v>7022100</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128589408</v>
       </c>
       <c r="B23" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3219,48 +3219,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128586312</v>
+        <v>128591228</v>
       </c>
       <c r="B25" t="n">
-        <v>91508</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447610</v>
+        <v>447721</v>
       </c>
       <c r="R25" t="n">
-        <v>7022251</v>
+        <v>7022210</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3289,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3326,10 +3335,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591228</v>
+        <v>128589765</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,29 +3363,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447721</v>
+        <v>447553</v>
       </c>
       <c r="R26" t="n">
-        <v>7022210</v>
+        <v>7022148</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,32 +3442,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128589765</v>
+        <v>128586312</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>91513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447553</v>
+        <v>447610</v>
       </c>
       <c r="R27" t="n">
-        <v>7022148</v>
+        <v>7022251</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91508</v>
+        <v>91809</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R28" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,22 +3649,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91804</v>
+        <v>91513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R29" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,12 +3761,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4118,48 +4118,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128854957</v>
+        <v>128859191</v>
       </c>
       <c r="B33" t="n">
-        <v>91508</v>
+        <v>98643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447477</v>
+        <v>447654</v>
       </c>
       <c r="R33" t="n">
-        <v>7022152</v>
+        <v>7022117</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4188,7 +4192,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4198,12 +4202,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,22 +4217,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128857221</v>
+        <v>128854957</v>
       </c>
       <c r="B34" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,24 +4258,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447579</v>
+        <v>447477</v>
       </c>
       <c r="R34" t="n">
-        <v>7022145</v>
+        <v>7022152</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,7 +4299,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4315,7 +4309,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,49 +4329,50 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128859191</v>
+        <v>128857221</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>91513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447654</v>
+        <v>447579</v>
       </c>
       <c r="R35" t="n">
-        <v>7022117</v>
+        <v>7022145</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4456,7 +4456,7 @@
         <v>128859166</v>
       </c>
       <c r="B36" t="n">
-        <v>75194</v>
+        <v>82990</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128859079</v>
+        <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447676</v>
+        <v>447467</v>
       </c>
       <c r="R37" t="n">
-        <v>7022093</v>
+        <v>7022162</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4645,7 +4645,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4660,60 +4665,64 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128854129</v>
+        <v>128857410</v>
       </c>
       <c r="B38" t="n">
-        <v>91508</v>
+        <v>98643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447467</v>
+        <v>447636</v>
       </c>
       <c r="R38" t="n">
-        <v>7022162</v>
+        <v>7022220</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4742,7 +4751,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4752,12 +4761,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4772,64 +4776,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128857410</v>
+        <v>128859079</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447636</v>
+        <v>447676</v>
       </c>
       <c r="R39" t="n">
-        <v>7022220</v>
+        <v>7022093</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95874</v>
+        <v>95881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>128859190</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128857488</v>
+        <v>128859400</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>92448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447669</v>
+        <v>447545</v>
       </c>
       <c r="R42" t="n">
-        <v>7022248</v>
+        <v>7022169</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,12 +5208,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,12 +5223,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5243,7 +5238,7 @@
         <v>128856170</v>
       </c>
       <c r="B43" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5352,32 +5347,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128859400</v>
+        <v>128857488</v>
       </c>
       <c r="B44" t="n">
-        <v>92443</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5387,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447545</v>
+        <v>447669</v>
       </c>
       <c r="R44" t="n">
-        <v>7022169</v>
+        <v>7022248</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5422,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5432,7 +5427,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,60 +5447,74 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128857090</v>
+        <v>128859234</v>
       </c>
       <c r="B45" t="n">
-        <v>91804</v>
+        <v>98643</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447519</v>
+        <v>447586</v>
       </c>
       <c r="R45" t="n">
-        <v>7022129</v>
+        <v>7022132</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5529,7 +5543,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5539,7 +5553,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5554,74 +5573,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128859234</v>
+        <v>128857090</v>
       </c>
       <c r="B46" t="n">
-        <v>98636</v>
+        <v>91809</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447586</v>
+        <v>447519</v>
       </c>
       <c r="R46" t="n">
-        <v>7022132</v>
+        <v>7022129</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5650,7 +5655,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5660,12 +5665,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5680,12 +5680,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
         <v>128859156</v>
       </c>
       <c r="B47" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>128857160</v>
       </c>
       <c r="B48" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>102101</v>
+        <v>102108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>128855978</v>
       </c>
       <c r="B50" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>128856768</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
         <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>128857503</v>
       </c>
       <c r="B53" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6494,32 +6494,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B54" t="n">
-        <v>80189</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R54" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6606,45 +6606,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>98643</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R55" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6676,7 +6685,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6686,12 +6695,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6718,54 +6727,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B56" t="n">
-        <v>98636</v>
+        <v>80094</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R56" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128590184</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128586050</v>
       </c>
       <c r="B6" t="n">
-        <v>91874</v>
+        <v>91879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128587720</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>128586443</v>
       </c>
       <c r="B8" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>128587013</v>
       </c>
       <c r="B9" t="n">
-        <v>82996</v>
+        <v>83001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,48 +1673,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128588534</v>
+        <v>128588025</v>
       </c>
       <c r="B11" t="n">
-        <v>80162</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447602</v>
+        <v>447724</v>
       </c>
       <c r="R11" t="n">
-        <v>7022100</v>
+        <v>7022011</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,57 +1789,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128588025</v>
+        <v>128588534</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>80167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447724</v>
+        <v>447602</v>
       </c>
       <c r="R12" t="n">
-        <v>7022011</v>
+        <v>7022100</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,7 +1899,7 @@
         <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>91800</v>
+        <v>91805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>79188</v>
+        <v>79193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B17" t="n">
-        <v>91515</v>
+        <v>78047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,42 +2349,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R17" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B18" t="n">
-        <v>78042</v>
+        <v>91520</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,37 +2456,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R18" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,7 +2560,7 @@
         <v>128586291</v>
       </c>
       <c r="B19" t="n">
-        <v>82996</v>
+        <v>83001</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128588406</v>
       </c>
       <c r="B21" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128589408</v>
       </c>
       <c r="B23" t="n">
-        <v>80169</v>
+        <v>80174</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128586312</v>
       </c>
       <c r="B25" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591228</v>
+        <v>128589765</v>
       </c>
       <c r="B26" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,29 +3354,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447721</v>
+        <v>447553</v>
       </c>
       <c r="R26" t="n">
-        <v>7022210</v>
+        <v>7022148</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3396,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3406,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,10 +3433,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B27" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,20 +3461,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R27" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4565,52 +4565,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128857410</v>
+        <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>91520</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447636</v>
+        <v>447467</v>
       </c>
       <c r="R37" t="n">
-        <v>7022220</v>
+        <v>7022162</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4639,7 +4635,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4649,7 +4645,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4664,22 +4665,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128854129</v>
+        <v>128859079</v>
       </c>
       <c r="B38" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,21 +4688,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4711,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447467</v>
+        <v>447676</v>
       </c>
       <c r="R38" t="n">
-        <v>7022162</v>
+        <v>7022093</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4746,7 +4747,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4756,12 +4757,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4776,60 +4772,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128859079</v>
+        <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>98651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447676</v>
+        <v>447636</v>
       </c>
       <c r="R39" t="n">
-        <v>7022093</v>
+        <v>7022220</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6149,54 +6149,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128857643</v>
+        <v>128856768</v>
       </c>
       <c r="B51" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447746</v>
+        <v>447518</v>
       </c>
       <c r="R51" t="n">
-        <v>7022160</v>
+        <v>7022171</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6219,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6229,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6263,52 +6254,61 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>98651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R52" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6494,32 +6494,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B54" t="n">
-        <v>80099</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R54" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6727,32 +6727,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128859089</v>
+        <v>128856585</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>80099</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447640</v>
+        <v>447500</v>
       </c>
       <c r="R56" t="n">
-        <v>7022114</v>
+        <v>7022174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128586050</v>
+        <v>128587720</v>
       </c>
       <c r="B6" t="n">
-        <v>91879</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447664</v>
+        <v>447673</v>
       </c>
       <c r="R6" t="n">
-        <v>7022270</v>
+        <v>7022084</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,21 +1209,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1240,32 +1225,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128587720</v>
+        <v>128586443</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>100839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447673</v>
+        <v>447624</v>
       </c>
       <c r="R7" t="n">
-        <v>7022084</v>
+        <v>7022238</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128586443</v>
+        <v>128586050</v>
       </c>
       <c r="B8" t="n">
-        <v>100839</v>
+        <v>91879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2062</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447624</v>
+        <v>447664</v>
       </c>
       <c r="R8" t="n">
-        <v>7022238</v>
+        <v>7022270</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,6 +1423,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1673,57 +1673,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128588025</v>
+        <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>80167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447724</v>
+        <v>447602</v>
       </c>
       <c r="R11" t="n">
-        <v>7022011</v>
+        <v>7022100</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,48 +1780,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128588534</v>
+        <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>80167</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447602</v>
+        <v>447724</v>
       </c>
       <c r="R12" t="n">
-        <v>7022100</v>
+        <v>7022011</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B17" t="n">
-        <v>78047</v>
+        <v>91520</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,37 +2349,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R17" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B18" t="n">
-        <v>91520</v>
+        <v>78047</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,42 +2461,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R18" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,48 +2557,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586291</v>
+        <v>128586645</v>
       </c>
       <c r="B19" t="n">
-        <v>83001</v>
+        <v>91520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447651</v>
+        <v>447644</v>
       </c>
       <c r="R19" t="n">
-        <v>7022237</v>
+        <v>7022249</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586645</v>
+        <v>128588406</v>
       </c>
       <c r="B20" t="n">
-        <v>91520</v>
+        <v>83010</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,42 +2680,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447644</v>
+        <v>447602</v>
       </c>
       <c r="R20" t="n">
-        <v>7022249</v>
+        <v>7022100</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,32 +2776,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588406</v>
+        <v>128586291</v>
       </c>
       <c r="B21" t="n">
-        <v>83010</v>
+        <v>83001</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447602</v>
+        <v>447651</v>
       </c>
       <c r="R21" t="n">
-        <v>7022100</v>
+        <v>7022237</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3219,48 +3219,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128586312</v>
+        <v>128591228</v>
       </c>
       <c r="B25" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447610</v>
+        <v>447721</v>
       </c>
       <c r="R25" t="n">
-        <v>7022251</v>
+        <v>7022210</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3289,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,57 +3442,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591228</v>
+        <v>128586312</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>91520</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447721</v>
+        <v>447610</v>
       </c>
       <c r="R27" t="n">
-        <v>7022210</v>
+        <v>7022251</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3552,7 +3552,7 @@
         <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>128857221</v>
       </c>
       <c r="B34" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95889</v>
+        <v>95894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B42" t="n">
-        <v>92456</v>
+        <v>91978</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R42" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,7 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5223,44 +5228,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B43" t="n">
-        <v>91975</v>
+        <v>92461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5270,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R43" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5315,12 +5320,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5335,12 +5335,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5459,48 +5459,62 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128857090</v>
+        <v>128859234</v>
       </c>
       <c r="B45" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447519</v>
+        <v>447586</v>
       </c>
       <c r="R45" t="n">
-        <v>7022129</v>
+        <v>7022132</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5529,7 +5543,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5539,7 +5553,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5554,74 +5573,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128859234</v>
+        <v>128857090</v>
       </c>
       <c r="B46" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447586</v>
+        <v>447519</v>
       </c>
       <c r="R46" t="n">
-        <v>7022132</v>
+        <v>7022129</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5650,7 +5655,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5660,12 +5665,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5680,12 +5680,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5802,7 +5802,7 @@
         <v>128857160</v>
       </c>
       <c r="B48" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>102116</v>
+        <v>102121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>128855978</v>
       </c>
       <c r="B50" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6149,45 +6149,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R51" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6219,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6229,12 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,61 +6263,52 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128857643</v>
+        <v>128856768</v>
       </c>
       <c r="B52" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447746</v>
+        <v>447518</v>
       </c>
       <c r="R52" t="n">
-        <v>7022160</v>
+        <v>7022171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6606,54 +6606,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B55" t="n">
-        <v>98651</v>
+        <v>80099</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R55" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6685,7 +6676,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6695,12 +6686,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6727,45 +6718,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128856585</v>
+        <v>128857763</v>
       </c>
       <c r="B56" t="n">
-        <v>80099</v>
+        <v>98656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447500</v>
+        <v>447780</v>
       </c>
       <c r="R56" t="n">
-        <v>7022174</v>
+        <v>7022116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103173</v>
+        <v>103178</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128586544</v>
+        <v>128589328</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>80141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447634</v>
+        <v>447558</v>
       </c>
       <c r="R2" t="n">
-        <v>7022247</v>
+        <v>7022168</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128589328</v>
+        <v>128586544</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447558</v>
+        <v>447634</v>
       </c>
       <c r="R3" t="n">
-        <v>7022168</v>
+        <v>7022247</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>128586845</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>128590184</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587720</v>
+        <v>128586443</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>100847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447673</v>
+        <v>447624</v>
       </c>
       <c r="R6" t="n">
-        <v>7022084</v>
+        <v>7022238</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,32 +1225,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128586443</v>
+        <v>128587013</v>
       </c>
       <c r="B7" t="n">
-        <v>100839</v>
+        <v>83002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447624</v>
+        <v>447663</v>
       </c>
       <c r="R7" t="n">
-        <v>7022238</v>
+        <v>7022106</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1340,7 @@
         <v>128586050</v>
       </c>
       <c r="B8" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128587013</v>
+        <v>128587720</v>
       </c>
       <c r="B9" t="n">
-        <v>83001</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447663</v>
+        <v>447673</v>
       </c>
       <c r="R9" t="n">
-        <v>7022106</v>
+        <v>7022084</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,12 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
         <v>128589559</v>
       </c>
       <c r="B10" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128588534</v>
       </c>
       <c r="B11" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128588025</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128586567</v>
       </c>
       <c r="B13" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>128592777</v>
       </c>
       <c r="B14" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>128586927</v>
       </c>
       <c r="B15" t="n">
-        <v>79193</v>
+        <v>79194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>128591182</v>
       </c>
       <c r="B16" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>128587761</v>
       </c>
       <c r="B17" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>128591149</v>
       </c>
       <c r="B18" t="n">
-        <v>78047</v>
+        <v>78048</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128586645</v>
+        <v>128588406</v>
       </c>
       <c r="B19" t="n">
-        <v>91520</v>
+        <v>83011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,42 +2568,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447644</v>
+        <v>447602</v>
       </c>
       <c r="R19" t="n">
-        <v>7022249</v>
+        <v>7022100</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2627,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2637,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,10 +2664,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128588406</v>
+        <v>128586645</v>
       </c>
       <c r="B20" t="n">
-        <v>83010</v>
+        <v>91526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,37 +2675,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447602</v>
+        <v>447644</v>
       </c>
       <c r="R20" t="n">
-        <v>7022100</v>
+        <v>7022249</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2779,7 +2779,7 @@
         <v>128586291</v>
       </c>
       <c r="B21" t="n">
-        <v>83001</v>
+        <v>83002</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>128591273</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>128589408</v>
       </c>
       <c r="B23" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>128589039</v>
       </c>
       <c r="B24" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3219,57 +3219,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591228</v>
+        <v>128586312</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>91526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447721</v>
+        <v>447610</v>
       </c>
       <c r="R25" t="n">
-        <v>7022210</v>
+        <v>7022251</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3298,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3338,7 +3329,7 @@
         <v>128589765</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,48 +3433,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128586312</v>
+        <v>128591228</v>
       </c>
       <c r="B27" t="n">
-        <v>91520</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447610</v>
+        <v>447721</v>
       </c>
       <c r="R27" t="n">
-        <v>7022251</v>
+        <v>7022210</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3552,7 +3552,7 @@
         <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128854957</v>
+        <v>128857221</v>
       </c>
       <c r="B33" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4147,19 +4147,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447477</v>
+        <v>447579</v>
       </c>
       <c r="R33" t="n">
-        <v>7022152</v>
+        <v>7022145</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4188,7 +4193,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4198,12 +4203,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,22 +4218,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128857221</v>
+        <v>128854957</v>
       </c>
       <c r="B34" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,24 +4259,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447579</v>
+        <v>447477</v>
       </c>
       <c r="R34" t="n">
-        <v>7022145</v>
+        <v>7022152</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,7 +4300,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4315,7 +4310,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,12 +4330,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4345,7 +4345,7 @@
         <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>128859166</v>
       </c>
       <c r="B36" t="n">
-        <v>82995</v>
+        <v>82996</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4568,7 +4568,7 @@
         <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>128859079</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4787,7 +4787,7 @@
         <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95894</v>
+        <v>95897</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5010,7 +5010,7 @@
         <v>128859190</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5121,39 +5121,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B42" t="n">
-        <v>91978</v>
+        <v>92464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R42" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,12 +5208,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,44 +5223,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B43" t="n">
-        <v>92461</v>
+        <v>91981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5270,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R43" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5305,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,7 +5315,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5335,12 +5335,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5350,7 +5350,7 @@
         <v>128857488</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,62 +5459,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128859234</v>
+        <v>128857090</v>
       </c>
       <c r="B45" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447586</v>
+        <v>447519</v>
       </c>
       <c r="R45" t="n">
-        <v>7022132</v>
+        <v>7022129</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5543,7 +5529,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5553,12 +5539,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,60 +5554,74 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128857090</v>
+        <v>128859234</v>
       </c>
       <c r="B46" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447519</v>
+        <v>447586</v>
       </c>
       <c r="R46" t="n">
-        <v>7022129</v>
+        <v>7022132</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5655,7 +5650,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5665,7 +5660,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5680,12 +5680,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
         <v>128859156</v>
       </c>
       <c r="B47" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5799,38 +5799,47 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B48" t="n">
-        <v>91523</v>
+        <v>102124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5839,13 +5848,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R48" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5874,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5884,7 +5893,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,59 +5913,50 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>102121</v>
+        <v>91526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5960,13 +5965,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R49" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5995,7 +6000,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,12 +6010,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,57 +6025,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128855978</v>
+        <v>128857643</v>
       </c>
       <c r="B50" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447481</v>
+        <v>447746</v>
       </c>
       <c r="R50" t="n">
-        <v>7022155</v>
+        <v>7022160</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6107,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6117,12 +6126,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,61 +6151,52 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128857643</v>
+        <v>128855978</v>
       </c>
       <c r="B51" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447746</v>
+        <v>447481</v>
       </c>
       <c r="R51" t="n">
-        <v>7022160</v>
+        <v>7022155</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6273,7 +6273,7 @@
         <v>128856768</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6385,7 +6385,7 @@
         <v>128857503</v>
       </c>
       <c r="B53" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>128859089</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6599,52 +6599,61 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128856585</v>
+        <v>128857763</v>
       </c>
       <c r="B55" t="n">
-        <v>80099</v>
+        <v>98659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447500</v>
+        <v>447780</v>
       </c>
       <c r="R55" t="n">
-        <v>7022174</v>
+        <v>7022116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6676,7 +6685,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6686,12 +6695,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6718,54 +6727,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B56" t="n">
-        <v>98656</v>
+        <v>80100</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R56" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103178</v>
+        <v>103181</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128586443</v>
+        <v>128587013</v>
       </c>
       <c r="B6" t="n">
-        <v>100847</v>
+        <v>83002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>492</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447624</v>
+        <v>447663</v>
       </c>
       <c r="R6" t="n">
-        <v>7022238</v>
+        <v>7022106</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128587013</v>
+        <v>128586050</v>
       </c>
       <c r="B7" t="n">
-        <v>83002</v>
+        <v>91885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447663</v>
+        <v>447664</v>
       </c>
       <c r="R7" t="n">
-        <v>7022106</v>
+        <v>7022270</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,6 +1321,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1337,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128586050</v>
+        <v>128587720</v>
       </c>
       <c r="B8" t="n">
-        <v>91885</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447664</v>
+        <v>447673</v>
       </c>
       <c r="R8" t="n">
-        <v>7022270</v>
+        <v>7022084</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,21 +1443,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128587720</v>
+        <v>128586443</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>100847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447673</v>
+        <v>447624</v>
       </c>
       <c r="R9" t="n">
-        <v>7022084</v>
+        <v>7022238</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3219,32 +3219,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128586312</v>
+        <v>128589765</v>
       </c>
       <c r="B25" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447610</v>
+        <v>447553</v>
       </c>
       <c r="R25" t="n">
-        <v>7022251</v>
+        <v>7022148</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3326,7 +3326,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B26" t="n">
         <v>98659</v>
@@ -3354,20 +3354,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R26" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3396,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3406,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3433,57 +3442,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128591228</v>
+        <v>128586312</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447721</v>
+        <v>447610</v>
       </c>
       <c r="R27" t="n">
-        <v>7022210</v>
+        <v>7022251</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4118,7 +4118,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128857221</v>
+        <v>128854957</v>
       </c>
       <c r="B33" t="n">
         <v>91526</v>
@@ -4147,24 +4147,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447579</v>
+        <v>447477</v>
       </c>
       <c r="R33" t="n">
-        <v>7022145</v>
+        <v>7022152</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4193,7 +4188,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4203,7 +4198,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,19 +4218,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128854957</v>
+        <v>128857221</v>
       </c>
       <c r="B34" t="n">
         <v>91526</v>
@@ -4259,19 +4259,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447477</v>
+        <v>447579</v>
       </c>
       <c r="R34" t="n">
-        <v>7022152</v>
+        <v>7022145</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4300,7 +4305,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4310,12 +4315,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,12 +4330,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4558,17 +4558,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128854129</v>
+        <v>128859079</v>
       </c>
       <c r="B37" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447467</v>
+        <v>447676</v>
       </c>
       <c r="R37" t="n">
-        <v>7022162</v>
+        <v>7022093</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4645,12 +4645,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4665,60 +4660,64 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128859079</v>
+        <v>128857410</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447676</v>
+        <v>447636</v>
       </c>
       <c r="R38" t="n">
-        <v>7022093</v>
+        <v>7022220</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4747,7 +4746,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4757,7 +4756,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4777,59 +4776,55 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128857410</v>
+        <v>128854129</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447636</v>
+        <v>447467</v>
       </c>
       <c r="R39" t="n">
-        <v>7022220</v>
+        <v>7022162</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4858,7 +4853,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4863,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4883,12 +4883,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5121,39 +5121,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B42" t="n">
-        <v>92464</v>
+        <v>91981</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R42" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,7 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5223,44 +5228,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128856170</v>
+        <v>128857488</v>
       </c>
       <c r="B43" t="n">
-        <v>91981</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5270,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447486</v>
+        <v>447669</v>
       </c>
       <c r="R43" t="n">
-        <v>7022172</v>
+        <v>7022248</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5315,12 +5320,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,39 +5345,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128857488</v>
+        <v>128859400</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>92464</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,13 +5387,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447669</v>
+        <v>447545</v>
       </c>
       <c r="R44" t="n">
-        <v>7022248</v>
+        <v>7022169</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5417,7 +5422,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5427,12 +5432,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5799,47 +5799,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B48" t="n">
-        <v>102124</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5848,13 +5839,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R48" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5883,7 +5874,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,12 +5884,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,50 +5899,59 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>91526</v>
+        <v>102124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5965,13 +5960,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R49" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6000,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6010,7 +6005,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6494,32 +6494,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128859089</v>
+        <v>128856585</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>80100</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447640</v>
+        <v>447500</v>
       </c>
       <c r="R54" t="n">
-        <v>7022114</v>
+        <v>7022174</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6727,32 +6727,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B56" t="n">
-        <v>80100</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R56" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128589328</v>
+        <v>128586544</v>
       </c>
       <c r="B2" t="n">
-        <v>80141</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447558</v>
+        <v>447634</v>
       </c>
       <c r="R2" t="n">
-        <v>7022168</v>
+        <v>7022247</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128586544</v>
+        <v>128589328</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>80141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447634</v>
+        <v>447558</v>
       </c>
       <c r="R3" t="n">
-        <v>7022247</v>
+        <v>7022168</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1896,32 +1896,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128586567</v>
+        <v>128592777</v>
       </c>
       <c r="B13" t="n">
-        <v>91811</v>
+        <v>92464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447644</v>
+        <v>447658</v>
       </c>
       <c r="R13" t="n">
-        <v>7022249</v>
+        <v>7022305</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128592777</v>
+        <v>128586567</v>
       </c>
       <c r="B14" t="n">
-        <v>92464</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447658</v>
+        <v>447644</v>
       </c>
       <c r="R14" t="n">
-        <v>7022305</v>
+        <v>7022249</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128587761</v>
+        <v>128591149</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>78048</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,42 +2349,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447673</v>
+        <v>447711</v>
       </c>
       <c r="R17" t="n">
-        <v>7022084</v>
+        <v>7022219</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2423,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128591149</v>
+        <v>128587761</v>
       </c>
       <c r="B18" t="n">
-        <v>78048</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,37 +2456,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447711</v>
+        <v>447673</v>
       </c>
       <c r="R18" t="n">
-        <v>7022219</v>
+        <v>7022084</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3219,7 +3219,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128589765</v>
+        <v>128591228</v>
       </c>
       <c r="B25" t="n">
         <v>98659</v>
@@ -3247,20 +3247,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447553</v>
+        <v>447721</v>
       </c>
       <c r="R25" t="n">
-        <v>7022148</v>
+        <v>7022210</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3289,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3299,7 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3326,7 +3335,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128591228</v>
+        <v>128589765</v>
       </c>
       <c r="B26" t="n">
         <v>98659</v>
@@ -3354,29 +3363,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447721</v>
+        <v>447553</v>
       </c>
       <c r="R26" t="n">
-        <v>7022210</v>
+        <v>7022148</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3549,32 +3549,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128857156</v>
+        <v>128859396</v>
       </c>
       <c r="B28" t="n">
-        <v>91811</v>
+        <v>100847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447528</v>
+        <v>447545</v>
       </c>
       <c r="R28" t="n">
-        <v>7022120</v>
+        <v>7022169</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,17 +3649,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3667,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R29" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3736,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,44 +3756,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128859396</v>
+        <v>128856217</v>
       </c>
       <c r="B30" t="n">
-        <v>100847</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3808,13 +3803,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447545</v>
+        <v>447498</v>
       </c>
       <c r="R30" t="n">
-        <v>7022169</v>
+        <v>7022166</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3853,7 +3848,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,7 +3868,7 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4118,48 +4118,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128854957</v>
+        <v>128859191</v>
       </c>
       <c r="B33" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447477</v>
+        <v>447654</v>
       </c>
       <c r="R33" t="n">
-        <v>7022152</v>
+        <v>7022117</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4188,7 +4192,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4198,12 +4202,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,19 +4217,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128857221</v>
+        <v>128854957</v>
       </c>
       <c r="B34" t="n">
         <v>91526</v>
@@ -4259,24 +4258,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447579</v>
+        <v>447477</v>
       </c>
       <c r="R34" t="n">
-        <v>7022145</v>
+        <v>7022152</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,7 +4299,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4315,7 +4309,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,49 +4329,50 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128859191</v>
+        <v>128857221</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447654</v>
+        <v>447579</v>
       </c>
       <c r="R35" t="n">
-        <v>7022117</v>
+        <v>7022145</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B42" t="n">
-        <v>91981</v>
+        <v>92464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R42" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,12 +5208,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,44 +5223,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128857488</v>
+        <v>128856170</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>91981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5270,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447669</v>
+        <v>447486</v>
       </c>
       <c r="R43" t="n">
-        <v>7022248</v>
+        <v>7022172</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5305,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,12 +5315,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5345,39 +5340,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128859400</v>
+        <v>128857488</v>
       </c>
       <c r="B44" t="n">
-        <v>92464</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5387,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447545</v>
+        <v>447669</v>
       </c>
       <c r="R44" t="n">
-        <v>7022169</v>
+        <v>7022248</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5422,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5432,7 +5427,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6037,54 +6037,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128857643</v>
+        <v>128855978</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447746</v>
+        <v>447481</v>
       </c>
       <c r="R50" t="n">
-        <v>7022160</v>
+        <v>7022155</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6107,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,12 +6117,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6151,17 +6142,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128855978</v>
+        <v>128856768</v>
       </c>
       <c r="B51" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,21 +6160,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6193,10 +6184,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447481</v>
+        <v>447518</v>
       </c>
       <c r="R51" t="n">
-        <v>7022155</v>
+        <v>7022171</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6219,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6229,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6263,52 +6254,61 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R52" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3549,32 +3549,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128859396</v>
+        <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>100847</v>
+        <v>91811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447545</v>
+        <v>447528</v>
       </c>
       <c r="R28" t="n">
-        <v>7022169</v>
+        <v>7022120</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,7 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,17 +3654,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3667,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R29" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,44 +3761,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128856217</v>
+        <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>100847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3803,13 +3808,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447498</v>
+        <v>447545</v>
       </c>
       <c r="R30" t="n">
-        <v>7022166</v>
+        <v>7022169</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,12 +3853,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,7 +3868,7 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4118,52 +4118,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128859191</v>
+        <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447654</v>
+        <v>447477</v>
       </c>
       <c r="R33" t="n">
-        <v>7022117</v>
+        <v>7022152</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4192,7 +4188,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4202,7 +4198,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,19 +4218,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128854957</v>
+        <v>128857221</v>
       </c>
       <c r="B34" t="n">
         <v>91526</v>
@@ -4258,19 +4259,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447477</v>
+        <v>447579</v>
       </c>
       <c r="R34" t="n">
-        <v>7022152</v>
+        <v>7022145</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4299,7 +4305,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4309,12 +4315,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4329,50 +4330,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128857221</v>
+        <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447579</v>
+        <v>447654</v>
       </c>
       <c r="R35" t="n">
-        <v>7022145</v>
+        <v>7022117</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4565,10 +4565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128859079</v>
+        <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447676</v>
+        <v>447467</v>
       </c>
       <c r="R37" t="n">
-        <v>7022093</v>
+        <v>7022162</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4645,7 +4645,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4660,64 +4665,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128857410</v>
+        <v>128859079</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447636</v>
+        <v>447676</v>
       </c>
       <c r="R38" t="n">
-        <v>7022220</v>
+        <v>7022093</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4746,7 +4747,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4756,7 +4757,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4776,55 +4777,59 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128854129</v>
+        <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447467</v>
+        <v>447636</v>
       </c>
       <c r="R39" t="n">
-        <v>7022162</v>
+        <v>7022220</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4853,7 +4858,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4863,12 +4868,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4883,12 +4883,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B42" t="n">
-        <v>92464</v>
+        <v>91981</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R42" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,7 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5223,44 +5228,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128856170</v>
+        <v>128857488</v>
       </c>
       <c r="B43" t="n">
-        <v>91981</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5270,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447486</v>
+        <v>447669</v>
       </c>
       <c r="R43" t="n">
-        <v>7022172</v>
+        <v>7022248</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5315,12 +5320,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,39 +5345,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128857488</v>
+        <v>128859400</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>92464</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,13 +5387,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447669</v>
+        <v>447545</v>
       </c>
       <c r="R44" t="n">
-        <v>7022248</v>
+        <v>7022169</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5417,7 +5422,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5427,12 +5432,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5799,38 +5799,47 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>102124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5839,13 +5848,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R48" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5874,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5884,7 +5893,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,59 +5913,50 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>102124</v>
+        <v>91526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5960,13 +5965,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R49" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5995,7 +6000,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,12 +6010,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6494,32 +6494,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B54" t="n">
-        <v>80100</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R54" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6606,54 +6606,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B55" t="n">
-        <v>98659</v>
+        <v>80100</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R55" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6685,7 +6676,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6695,12 +6686,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6727,45 +6718,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R56" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B28" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R28" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,22 +3649,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R29" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,12 +3761,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>128857221</v>
       </c>
       <c r="B34" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>128859166</v>
       </c>
       <c r="B36" t="n">
-        <v>82996</v>
+        <v>83000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128854129</v>
+        <v>128859079</v>
       </c>
       <c r="B37" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447467</v>
+        <v>447676</v>
       </c>
       <c r="R37" t="n">
-        <v>7022162</v>
+        <v>7022093</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4645,12 +4645,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4665,22 +4660,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128859079</v>
+        <v>128854129</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,21 +4683,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,13 +4707,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447676</v>
+        <v>447467</v>
       </c>
       <c r="R38" t="n">
-        <v>7022093</v>
+        <v>7022162</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4747,7 +4742,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4757,7 +4752,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4772,12 +4772,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4787,7 +4787,7 @@
         <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95897</v>
+        <v>95907</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>128859190</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B42" t="n">
-        <v>91981</v>
+        <v>92471</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R42" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,12 +5208,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,12 +5223,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5243,7 +5238,7 @@
         <v>128857488</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5352,32 +5347,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B44" t="n">
-        <v>92464</v>
+        <v>91988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5387,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R44" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5422,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5432,7 +5427,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
         <v>128857090</v>
       </c>
       <c r="B45" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128859234</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>128859156</v>
       </c>
       <c r="B47" t="n">
-        <v>83003</v>
+        <v>83007</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5799,47 +5799,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B48" t="n">
-        <v>102124</v>
+        <v>91533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5848,13 +5839,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R48" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5883,7 +5874,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,12 +5884,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,50 +5899,59 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>91526</v>
+        <v>102134</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5965,13 +5960,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R49" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6000,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6010,7 +6005,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,57 +6025,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128855978</v>
+        <v>128857643</v>
       </c>
       <c r="B50" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447481</v>
+        <v>447746</v>
       </c>
       <c r="R50" t="n">
-        <v>7022155</v>
+        <v>7022160</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6107,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6117,12 +6126,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,17 +6151,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128856768</v>
+        <v>128855978</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>91818</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6160,21 +6169,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6184,10 +6193,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447518</v>
+        <v>447481</v>
       </c>
       <c r="R51" t="n">
-        <v>7022171</v>
+        <v>7022155</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6219,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6229,12 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,61 +6263,52 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128857643</v>
+        <v>128856768</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447746</v>
+        <v>447518</v>
       </c>
       <c r="R52" t="n">
-        <v>7022160</v>
+        <v>7022171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6385,7 +6385,7 @@
         <v>128857503</v>
       </c>
       <c r="B53" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>128859089</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>128856585</v>
       </c>
       <c r="B55" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>128857763</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103181</v>
+        <v>103191</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -6037,54 +6037,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128857643</v>
+        <v>128855978</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>91818</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447746</v>
+        <v>447481</v>
       </c>
       <c r="R50" t="n">
-        <v>7022160</v>
+        <v>7022155</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6107,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,12 +6117,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6151,17 +6142,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128855978</v>
+        <v>128856768</v>
       </c>
       <c r="B51" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,21 +6160,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6193,10 +6184,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447481</v>
+        <v>447518</v>
       </c>
       <c r="R51" t="n">
-        <v>7022155</v>
+        <v>7022171</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6219,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6229,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6263,52 +6254,61 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R52" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R28" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,22 +3649,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R29" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,12 +3761,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>128857221</v>
       </c>
       <c r="B34" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>128859166</v>
       </c>
       <c r="B36" t="n">
-        <v>83000</v>
+        <v>82990</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128859079</v>
+        <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447676</v>
+        <v>447467</v>
       </c>
       <c r="R37" t="n">
-        <v>7022093</v>
+        <v>7022162</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4645,7 +4645,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4660,60 +4665,64 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128854129</v>
+        <v>128857410</v>
       </c>
       <c r="B38" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447467</v>
+        <v>447636</v>
       </c>
       <c r="R38" t="n">
-        <v>7022162</v>
+        <v>7022220</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4742,7 +4751,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4752,12 +4761,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4772,64 +4776,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128857410</v>
+        <v>128859079</v>
       </c>
       <c r="B39" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447636</v>
+        <v>447676</v>
       </c>
       <c r="R39" t="n">
-        <v>7022220</v>
+        <v>7022093</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95907</v>
+        <v>95914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>128859400</v>
       </c>
       <c r="B42" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>128856170</v>
       </c>
       <c r="B44" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>128857090</v>
       </c>
       <c r="B45" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128859234</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>128859156</v>
       </c>
       <c r="B47" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5799,38 +5799,47 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B48" t="n">
-        <v>91533</v>
+        <v>102141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5839,13 +5848,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R48" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5874,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5884,7 +5893,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,59 +5913,50 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>102134</v>
+        <v>91540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5960,13 +5965,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R49" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5995,7 +6000,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,12 +6010,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6040,7 +6040,7 @@
         <v>128855978</v>
       </c>
       <c r="B50" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
         <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6494,45 +6494,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R54" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6573,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6574,12 +6583,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6606,32 +6615,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B55" t="n">
-        <v>80104</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6641,10 +6650,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R55" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6676,7 +6685,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6686,12 +6695,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6718,54 +6727,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B56" t="n">
-        <v>98669</v>
+        <v>80104</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R56" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103191</v>
+        <v>103198</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B28" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R28" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,22 +3649,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R29" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,12 +3761,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>128857221</v>
       </c>
       <c r="B34" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>128859166</v>
       </c>
       <c r="B36" t="n">
-        <v>82990</v>
+        <v>82992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4565,48 +4565,52 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128854129</v>
+        <v>128857410</v>
       </c>
       <c r="B37" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447467</v>
+        <v>447636</v>
       </c>
       <c r="R37" t="n">
-        <v>7022162</v>
+        <v>7022220</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4635,7 +4639,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4645,12 +4649,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4665,64 +4664,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128857410</v>
+        <v>128854129</v>
       </c>
       <c r="B38" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447636</v>
+        <v>447467</v>
       </c>
       <c r="R38" t="n">
-        <v>7022220</v>
+        <v>7022162</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4751,7 +4746,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4761,7 +4756,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4776,12 +4776,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4791,7 +4791,7 @@
         <v>128859079</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>128859190</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B42" t="n">
-        <v>92478</v>
+        <v>91997</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R42" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,7 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5223,12 +5228,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5238,7 +5243,7 @@
         <v>128857488</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,32 +5352,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B44" t="n">
-        <v>91995</v>
+        <v>92480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,13 +5387,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R44" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5417,7 +5422,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5427,12 +5432,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
         <v>128857090</v>
       </c>
       <c r="B45" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128859234</v>
       </c>
       <c r="B46" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>128859156</v>
       </c>
       <c r="B47" t="n">
-        <v>82997</v>
+        <v>82999</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>128859403</v>
       </c>
       <c r="B48" t="n">
-        <v>102141</v>
+        <v>102143</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>128855978</v>
       </c>
       <c r="B50" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>128856768</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>128857503</v>
       </c>
       <c r="B53" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6494,54 +6494,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128857763</v>
+        <v>128859089</v>
       </c>
       <c r="B54" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447780</v>
+        <v>447640</v>
       </c>
       <c r="R54" t="n">
-        <v>7022116</v>
+        <v>7022114</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6573,7 +6564,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6583,12 +6574,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6615,45 +6606,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R55" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6730,7 +6730,7 @@
         <v>128856585</v>
       </c>
       <c r="B56" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103198</v>
+        <v>103200</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R28" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,22 +3649,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R29" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,12 +3761,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128856170</v>
+        <v>128857488</v>
       </c>
       <c r="B42" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447486</v>
+        <v>447669</v>
       </c>
       <c r="R42" t="n">
-        <v>7022172</v>
+        <v>7022248</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5233,39 +5233,39 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128857488</v>
+        <v>128856170</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>91997</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447669</v>
+        <v>447486</v>
       </c>
       <c r="R43" t="n">
-        <v>7022248</v>
+        <v>7022172</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5799,47 +5799,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B48" t="n">
-        <v>102143</v>
+        <v>91542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5848,13 +5839,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R48" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5883,7 +5874,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,12 +5884,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,50 +5899,59 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>91542</v>
+        <v>102143</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5965,13 +5960,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R49" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6000,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6010,7 +6005,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,57 +6025,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128855978</v>
+        <v>128857643</v>
       </c>
       <c r="B50" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447481</v>
+        <v>447746</v>
       </c>
       <c r="R50" t="n">
-        <v>7022155</v>
+        <v>7022160</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6107,7 +6116,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6117,12 +6126,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,17 +6151,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128856768</v>
+        <v>128855978</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6160,21 +6169,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6184,10 +6193,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447518</v>
+        <v>447481</v>
       </c>
       <c r="R51" t="n">
-        <v>7022171</v>
+        <v>7022155</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6219,7 +6228,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6229,12 +6238,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,61 +6263,52 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128857643</v>
+        <v>128856768</v>
       </c>
       <c r="B52" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447746</v>
+        <v>447518</v>
       </c>
       <c r="R52" t="n">
-        <v>7022160</v>
+        <v>7022171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6606,54 +6606,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B55" t="n">
-        <v>98678</v>
+        <v>80106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R55" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6685,7 +6676,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6695,12 +6686,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6727,45 +6718,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128856585</v>
+        <v>128857763</v>
       </c>
       <c r="B56" t="n">
-        <v>80106</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447500</v>
+        <v>447780</v>
       </c>
       <c r="R56" t="n">
-        <v>7022174</v>
+        <v>7022116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3549,32 +3549,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128857156</v>
+        <v>128859396</v>
       </c>
       <c r="B28" t="n">
-        <v>91827</v>
+        <v>100866</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447528</v>
+        <v>447545</v>
       </c>
       <c r="R28" t="n">
-        <v>7022120</v>
+        <v>7022169</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,7 +3649,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3773,32 +3768,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128859396</v>
+        <v>128857156</v>
       </c>
       <c r="B30" t="n">
-        <v>100866</v>
+        <v>91827</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3808,13 +3803,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447545</v>
+        <v>447528</v>
       </c>
       <c r="R30" t="n">
-        <v>7022169</v>
+        <v>7022120</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3853,7 +3848,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128854129</v>
+        <v>128859079</v>
       </c>
       <c r="B38" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447467</v>
+        <v>447676</v>
       </c>
       <c r="R38" t="n">
-        <v>7022162</v>
+        <v>7022093</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4756,12 +4756,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4776,22 +4771,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128859079</v>
+        <v>128854129</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4799,21 +4794,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4823,13 +4818,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447676</v>
+        <v>447467</v>
       </c>
       <c r="R39" t="n">
-        <v>7022093</v>
+        <v>7022162</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4858,7 +4853,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4863,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4883,12 +4883,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128857488</v>
+        <v>128859400</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>92480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447669</v>
+        <v>447545</v>
       </c>
       <c r="R42" t="n">
-        <v>7022248</v>
+        <v>7022169</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,12 +5208,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,44 +5223,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128856170</v>
+        <v>128857488</v>
       </c>
       <c r="B43" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5270,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447486</v>
+        <v>447669</v>
       </c>
       <c r="R43" t="n">
-        <v>7022172</v>
+        <v>7022248</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5305,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,12 +5315,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5345,39 +5340,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B44" t="n">
-        <v>92480</v>
+        <v>91997</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5387,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R44" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5422,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5432,7 +5427,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5799,38 +5799,47 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B48" t="n">
-        <v>91542</v>
+        <v>102143</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5839,13 +5848,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R48" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5874,7 +5883,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5884,7 +5893,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,59 +5913,50 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>102143</v>
+        <v>91542</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5960,13 +5965,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R49" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5995,7 +6000,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,12 +6010,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6494,32 +6494,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128859089</v>
+        <v>128856585</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>80106</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447640</v>
+        <v>447500</v>
       </c>
       <c r="R54" t="n">
-        <v>7022114</v>
+        <v>7022174</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6606,45 +6606,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128856585</v>
+        <v>128857763</v>
       </c>
       <c r="B55" t="n">
-        <v>80106</v>
+        <v>98678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447500</v>
+        <v>447780</v>
       </c>
       <c r="R55" t="n">
-        <v>7022174</v>
+        <v>7022116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6676,7 +6685,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6686,12 +6695,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6718,54 +6727,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128857763</v>
+        <v>128859089</v>
       </c>
       <c r="B56" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447780</v>
+        <v>447640</v>
       </c>
       <c r="R56" t="n">
-        <v>7022116</v>
+        <v>7022114</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3552,7 +3552,7 @@
         <v>128859396</v>
       </c>
       <c r="B28" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B29" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R29" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,22 +3756,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128857156</v>
+        <v>128856217</v>
       </c>
       <c r="B30" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,21 +3779,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447528</v>
+        <v>447498</v>
       </c>
       <c r="R30" t="n">
-        <v>7022120</v>
+        <v>7022166</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,12 +3868,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4121,7 +4121,7 @@
         <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>128857221</v>
       </c>
       <c r="B34" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>128857410</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128859079</v>
+        <v>128854129</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447676</v>
+        <v>447467</v>
       </c>
       <c r="R38" t="n">
-        <v>7022093</v>
+        <v>7022162</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4756,7 +4756,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4771,22 +4776,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128854129</v>
+        <v>128859079</v>
       </c>
       <c r="B39" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,21 +4799,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4818,13 +4823,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447467</v>
+        <v>447676</v>
       </c>
       <c r="R39" t="n">
-        <v>7022162</v>
+        <v>7022093</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4853,7 +4858,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4863,12 +4868,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4883,12 +4883,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95916</v>
+        <v>95942</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,39 +5121,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128859400</v>
+        <v>128857488</v>
       </c>
       <c r="B42" t="n">
-        <v>92480</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447545</v>
+        <v>447669</v>
       </c>
       <c r="R42" t="n">
-        <v>7022169</v>
+        <v>7022248</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,7 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5223,44 +5228,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128857488</v>
+        <v>128856170</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>91992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5270,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447669</v>
+        <v>447486</v>
       </c>
       <c r="R43" t="n">
-        <v>7022248</v>
+        <v>7022172</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5315,12 +5320,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,39 +5345,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B44" t="n">
-        <v>91997</v>
+        <v>92494</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,13 +5387,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R44" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5417,7 +5422,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5427,12 +5432,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,60 +5447,74 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128857090</v>
+        <v>128859234</v>
       </c>
       <c r="B45" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447519</v>
+        <v>447586</v>
       </c>
       <c r="R45" t="n">
-        <v>7022129</v>
+        <v>7022132</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5529,7 +5543,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5539,7 +5553,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5554,74 +5573,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128859234</v>
+        <v>128857090</v>
       </c>
       <c r="B46" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447586</v>
+        <v>447519</v>
       </c>
       <c r="R46" t="n">
-        <v>7022132</v>
+        <v>7022129</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5650,7 +5655,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5660,12 +5665,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5680,12 +5680,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5802,7 +5802,7 @@
         <v>128859403</v>
       </c>
       <c r="B48" t="n">
-        <v>102143</v>
+        <v>102169</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>128857160</v>
       </c>
       <c r="B49" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>128857643</v>
       </c>
       <c r="B50" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>128855978</v>
       </c>
       <c r="B51" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6494,32 +6494,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B54" t="n">
-        <v>80106</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R54" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6606,54 +6606,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B55" t="n">
-        <v>98678</v>
+        <v>80106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R55" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6685,7 +6676,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6695,12 +6686,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,52 +6711,61 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R56" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103200</v>
+        <v>103226</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3549,32 +3549,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128859396</v>
+        <v>128856217</v>
       </c>
       <c r="B28" t="n">
-        <v>100892</v>
+        <v>91540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447545</v>
+        <v>447498</v>
       </c>
       <c r="R28" t="n">
-        <v>7022169</v>
+        <v>7022166</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,7 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3644,44 +3649,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128857156</v>
+        <v>128859396</v>
       </c>
       <c r="B29" t="n">
-        <v>91837</v>
+        <v>100894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3691,13 +3696,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447528</v>
+        <v>447545</v>
       </c>
       <c r="R29" t="n">
-        <v>7022120</v>
+        <v>7022169</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3726,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3736,12 +3741,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,21 +3779,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R30" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,12 +3868,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4565,52 +4565,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128857410</v>
+        <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447636</v>
+        <v>447467</v>
       </c>
       <c r="R37" t="n">
-        <v>7022220</v>
+        <v>7022162</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4639,7 +4635,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4649,7 +4645,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4664,22 +4665,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128854129</v>
+        <v>128859079</v>
       </c>
       <c r="B38" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,21 +4688,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4711,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447467</v>
+        <v>447676</v>
       </c>
       <c r="R38" t="n">
-        <v>7022162</v>
+        <v>7022093</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4746,7 +4747,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4756,12 +4757,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4776,60 +4772,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128859079</v>
+        <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447676</v>
+        <v>447636</v>
       </c>
       <c r="R39" t="n">
-        <v>7022093</v>
+        <v>7022220</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95942</v>
+        <v>95943</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5240,32 +5240,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B43" t="n">
-        <v>91992</v>
+        <v>92495</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R43" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,12 +5320,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,44 +5335,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128859400</v>
+        <v>128856170</v>
       </c>
       <c r="B44" t="n">
-        <v>92494</v>
+        <v>91993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5387,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447545</v>
+        <v>447486</v>
       </c>
       <c r="R44" t="n">
-        <v>7022169</v>
+        <v>7022172</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5422,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5432,7 +5427,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,74 +5447,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128859234</v>
+        <v>128857090</v>
       </c>
       <c r="B45" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447586</v>
+        <v>447519</v>
       </c>
       <c r="R45" t="n">
-        <v>7022132</v>
+        <v>7022129</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5543,7 +5529,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5553,12 +5539,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,60 +5554,74 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128857090</v>
+        <v>128859234</v>
       </c>
       <c r="B46" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447519</v>
+        <v>447586</v>
       </c>
       <c r="R46" t="n">
-        <v>7022129</v>
+        <v>7022132</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5655,7 +5650,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5665,7 +5660,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5680,12 +5680,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5802,7 +5802,7 @@
         <v>128859403</v>
       </c>
       <c r="B48" t="n">
-        <v>102169</v>
+        <v>102171</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6037,54 +6037,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128857643</v>
+        <v>128855978</v>
       </c>
       <c r="B50" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447746</v>
+        <v>447481</v>
       </c>
       <c r="R50" t="n">
-        <v>7022160</v>
+        <v>7022155</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6116,7 +6107,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6126,12 +6117,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6151,17 +6142,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128855978</v>
+        <v>128856768</v>
       </c>
       <c r="B51" t="n">
-        <v>91837</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,21 +6160,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6193,10 +6184,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447481</v>
+        <v>447518</v>
       </c>
       <c r="R51" t="n">
-        <v>7022155</v>
+        <v>7022171</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6228,7 +6219,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6238,12 +6229,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6263,52 +6254,61 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128856768</v>
+        <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447518</v>
+        <v>447746</v>
       </c>
       <c r="R52" t="n">
-        <v>7022171</v>
+        <v>7022160</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6494,45 +6494,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128859089</v>
+        <v>128857763</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447640</v>
+        <v>447780</v>
       </c>
       <c r="R54" t="n">
-        <v>7022114</v>
+        <v>7022116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,7 +6573,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6574,12 +6583,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6606,32 +6615,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B55" t="n">
-        <v>80106</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6641,10 +6650,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R55" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6676,7 +6685,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6686,12 +6695,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6711,61 +6720,52 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128857763</v>
+        <v>128856585</v>
       </c>
       <c r="B56" t="n">
-        <v>98704</v>
+        <v>80106</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447780</v>
+        <v>447500</v>
       </c>
       <c r="R56" t="n">
-        <v>7022116</v>
+        <v>7022174</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103226</v>
+        <v>103228</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3549,10 +3549,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128856217</v>
+        <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447498</v>
+        <v>447528</v>
       </c>
       <c r="R28" t="n">
-        <v>7022166</v>
+        <v>7022120</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,44 +3649,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128859396</v>
+        <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>100894</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,13 +3696,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447545</v>
+        <v>447498</v>
       </c>
       <c r="R29" t="n">
-        <v>7022169</v>
+        <v>7022166</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3741,7 +3741,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3756,7 +3761,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3768,32 +3773,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128857156</v>
+        <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>91838</v>
+        <v>100895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3803,13 +3808,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447528</v>
+        <v>447545</v>
       </c>
       <c r="R30" t="n">
-        <v>7022120</v>
+        <v>7022169</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3848,12 +3853,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,48 +4118,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128854957</v>
+        <v>128859191</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447477</v>
+        <v>447654</v>
       </c>
       <c r="R33" t="n">
-        <v>7022152</v>
+        <v>7022117</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4188,7 +4192,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4198,12 +4202,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,19 +4217,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128857221</v>
+        <v>128854957</v>
       </c>
       <c r="B34" t="n">
         <v>91540</v>
@@ -4259,24 +4258,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447579</v>
+        <v>447477</v>
       </c>
       <c r="R34" t="n">
-        <v>7022145</v>
+        <v>7022152</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,7 +4299,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4315,7 +4309,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,49 +4329,50 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128859191</v>
+        <v>128857221</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447654</v>
+        <v>447579</v>
       </c>
       <c r="R35" t="n">
-        <v>7022117</v>
+        <v>7022145</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4787,7 +4787,7 @@
         <v>128857410</v>
       </c>
       <c r="B39" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95943</v>
+        <v>95944</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5128,32 +5128,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128857488</v>
+        <v>128856170</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>91993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447669</v>
+        <v>447486</v>
       </c>
       <c r="R42" t="n">
-        <v>7022248</v>
+        <v>7022172</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5233,39 +5233,39 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128859400</v>
+        <v>128857488</v>
       </c>
       <c r="B43" t="n">
-        <v>92495</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447545</v>
+        <v>447669</v>
       </c>
       <c r="R43" t="n">
-        <v>7022169</v>
+        <v>7022248</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,7 +5320,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5335,44 +5340,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128856170</v>
+        <v>128859400</v>
       </c>
       <c r="B44" t="n">
-        <v>91993</v>
+        <v>92495</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,13 +5387,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447486</v>
+        <v>447545</v>
       </c>
       <c r="R44" t="n">
-        <v>7022172</v>
+        <v>7022169</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5417,7 +5422,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5427,12 +5432,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5569,7 +5569,7 @@
         <v>128859234</v>
       </c>
       <c r="B46" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5799,47 +5799,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128859403</v>
+        <v>128857160</v>
       </c>
       <c r="B48" t="n">
-        <v>102171</v>
+        <v>91540</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5848,13 +5839,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447541</v>
+        <v>447528</v>
       </c>
       <c r="R48" t="n">
-        <v>7022174</v>
+        <v>7022120</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5883,7 +5874,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,12 +5884,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,50 +5899,59 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128857160</v>
+        <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>102172</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5965,13 +5960,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447528</v>
+        <v>447541</v>
       </c>
       <c r="R49" t="n">
-        <v>7022120</v>
+        <v>7022174</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6000,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6010,7 +6005,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
         <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>128857763</v>
       </c>
       <c r="B54" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6615,32 +6615,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128859089</v>
+        <v>128856585</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>80106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447640</v>
+        <v>447500</v>
       </c>
       <c r="R55" t="n">
-        <v>7022114</v>
+        <v>7022174</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6727,32 +6727,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128856585</v>
+        <v>128859089</v>
       </c>
       <c r="B56" t="n">
-        <v>80106</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447500</v>
+        <v>447640</v>
       </c>
       <c r="R56" t="n">
-        <v>7022174</v>
+        <v>7022114</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103228</v>
+        <v>103229</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -3552,7 +3552,7 @@
         <v>128857156</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>128856217</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>128859396</v>
       </c>
       <c r="B30" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>128858970</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>128854816</v>
       </c>
       <c r="B32" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4118,52 +4118,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128859191</v>
+        <v>128854957</v>
       </c>
       <c r="B33" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447654</v>
+        <v>447477</v>
       </c>
       <c r="R33" t="n">
-        <v>7022117</v>
+        <v>7022152</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4192,7 +4188,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4202,7 +4198,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,22 +4218,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128854957</v>
+        <v>128857221</v>
       </c>
       <c r="B34" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4258,19 +4259,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447477</v>
+        <v>447579</v>
       </c>
       <c r="R34" t="n">
-        <v>7022152</v>
+        <v>7022145</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4299,7 +4305,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4309,12 +4315,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4329,50 +4330,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128857221</v>
+        <v>128859191</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447579</v>
+        <v>447654</v>
       </c>
       <c r="R35" t="n">
-        <v>7022145</v>
+        <v>7022117</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4456,7 +4456,7 @@
         <v>128859166</v>
       </c>
       <c r="B36" t="n">
-        <v>82992</v>
+        <v>82996</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>128854129</v>
       </c>
       <c r="B37" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4677,48 +4677,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128859079</v>
+        <v>128857410</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447676</v>
+        <v>447636</v>
       </c>
       <c r="R38" t="n">
-        <v>7022093</v>
+        <v>7022220</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4747,7 +4751,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4777,59 +4781,55 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128857410</v>
+        <v>128859079</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447636</v>
+        <v>447676</v>
       </c>
       <c r="R39" t="n">
-        <v>7022220</v>
+        <v>7022093</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
         <v>128857152</v>
       </c>
       <c r="B40" t="n">
-        <v>95944</v>
+        <v>95948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>128859190</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>128856170</v>
       </c>
       <c r="B42" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5240,32 +5240,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128857488</v>
+        <v>128859400</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>92498</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447669</v>
+        <v>447545</v>
       </c>
       <c r="R43" t="n">
-        <v>7022248</v>
+        <v>7022169</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,12 +5320,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,44 +5335,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128859400</v>
+        <v>128857488</v>
       </c>
       <c r="B44" t="n">
-        <v>92495</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5387,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447545</v>
+        <v>447669</v>
       </c>
       <c r="R44" t="n">
-        <v>7022169</v>
+        <v>7022248</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5422,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5432,7 +5427,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,12 +5447,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
         <v>128857090</v>
       </c>
       <c r="B45" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>128859234</v>
       </c>
       <c r="B46" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>128859156</v>
       </c>
       <c r="B47" t="n">
-        <v>82999</v>
+        <v>83003</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>128857160</v>
       </c>
       <c r="B48" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>128859403</v>
       </c>
       <c r="B49" t="n">
-        <v>102172</v>
+        <v>102176</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128855978</v>
+        <v>128856768</v>
       </c>
       <c r="B50" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6048,21 +6048,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447481</v>
+        <v>447518</v>
       </c>
       <c r="R50" t="n">
-        <v>7022155</v>
+        <v>7022171</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,17 +6142,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128856768</v>
+        <v>128855978</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>91841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447518</v>
+        <v>447481</v>
       </c>
       <c r="R51" t="n">
-        <v>7022171</v>
+        <v>7022155</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6229,12 +6229,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
         <v>128857643</v>
       </c>
       <c r="B52" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>128857503</v>
       </c>
       <c r="B53" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>128857763</v>
       </c>
       <c r="B54" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>128856585</v>
       </c>
       <c r="B55" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>128859089</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>128859390</v>
       </c>
       <c r="B57" t="n">
-        <v>103229</v>
+        <v>103233</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6944,6 +6944,117 @@
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128857255</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>48</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>447578</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7022145</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -6949,7 +6949,7 @@
         <v>128857255</v>
       </c>
       <c r="B58" t="n">
-        <v>91818</v>
+        <v>91819</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -6949,7 +6949,7 @@
         <v>128857255</v>
       </c>
       <c r="B58" t="n">
-        <v>91819</v>
+        <v>91836</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -6949,7 +6949,7 @@
         <v>128857255</v>
       </c>
       <c r="B58" t="n">
-        <v>91852</v>
+        <v>91854</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -6949,7 +6949,7 @@
         <v>128857255</v>
       </c>
       <c r="B58" t="n">
-        <v>91854</v>
+        <v>91941</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128586544</v>
+        <v>128859403</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>102619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>22</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447634</v>
+        <v>447541</v>
       </c>
       <c r="R2" t="n">
-        <v>7022247</v>
+        <v>7022174</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +754,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På marken i rikare stråk i gammal kalkgranskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,60 +789,63 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128589328</v>
+        <v>128857255</v>
       </c>
       <c r="B3" t="n">
-        <v>80141</v>
+        <v>92123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447558</v>
+        <v>447578</v>
       </c>
       <c r="R3" t="n">
-        <v>7022168</v>
+        <v>7022145</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,35 +869,31 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,60 +905,55 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128586845</v>
+        <v>128859166</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>83292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447641</v>
+        <v>447658</v>
       </c>
       <c r="R4" t="n">
-        <v>7022206</v>
+        <v>7022103</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +977,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1012,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128590184</v>
+        <v>128859156</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447613</v>
+        <v>447663</v>
       </c>
       <c r="R5" t="n">
-        <v>7022111</v>
+        <v>7022108</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,22 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,17 +1124,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128587013</v>
+        <v>128586291</v>
       </c>
       <c r="B6" t="n">
-        <v>83002</v>
+        <v>83298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447663</v>
+        <v>447651</v>
       </c>
       <c r="R6" t="n">
-        <v>7022106</v>
+        <v>7022237</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1188,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128586050</v>
+        <v>128587013</v>
       </c>
       <c r="B7" t="n">
-        <v>91885</v>
+        <v>83298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1249,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447664</v>
+        <v>447663</v>
       </c>
       <c r="R7" t="n">
-        <v>7022270</v>
+        <v>7022106</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,21 +1334,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128587720</v>
+        <v>128586567</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447673</v>
+        <v>447644</v>
       </c>
       <c r="R8" t="n">
-        <v>7022084</v>
+        <v>7022249</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,32 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128586443</v>
+        <v>128855978</v>
       </c>
       <c r="B9" t="n">
-        <v>100847</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447624</v>
+        <v>447481</v>
       </c>
       <c r="R9" t="n">
-        <v>7022238</v>
+        <v>7022155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,22 +1522,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,44 +1557,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128589559</v>
+        <v>128857090</v>
       </c>
       <c r="B10" t="n">
-        <v>92464</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,13 +1604,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447547</v>
+        <v>447519</v>
       </c>
       <c r="R10" t="n">
-        <v>7022212</v>
+        <v>7022129</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1634,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128588534</v>
+        <v>128857156</v>
       </c>
       <c r="B11" t="n">
-        <v>80168</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,13 +1711,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447602</v>
+        <v>447528</v>
       </c>
       <c r="R11" t="n">
-        <v>7022100</v>
+        <v>7022120</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,22 +1741,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128588025</v>
+        <v>128586312</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,46 +1799,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447724</v>
+        <v>447610</v>
       </c>
       <c r="R12" t="n">
-        <v>7022011</v>
+        <v>7022251</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1868,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,48 +1895,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128592777</v>
+        <v>128586544</v>
       </c>
       <c r="B13" t="n">
-        <v>92464</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447658</v>
+        <v>447634</v>
       </c>
       <c r="R13" t="n">
-        <v>7022305</v>
+        <v>7022247</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128586567</v>
+        <v>128586645</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,24 +2018,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
@@ -2073,7 +2082,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2092,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,42 +2119,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128586927</v>
+        <v>128586845</v>
       </c>
       <c r="B15" t="n">
-        <v>79194</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2154,13 +2159,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447666</v>
+        <v>447641</v>
       </c>
       <c r="R15" t="n">
-        <v>7022106</v>
+        <v>7022206</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2189,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2199,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128591182</v>
+        <v>128587761</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,13 +2271,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447727</v>
+        <v>447673</v>
       </c>
       <c r="R16" t="n">
-        <v>7022210</v>
+        <v>7022084</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2311,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128591149</v>
+        <v>128589039</v>
       </c>
       <c r="B17" t="n">
-        <v>78048</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,37 +2354,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447711</v>
+        <v>447525</v>
       </c>
       <c r="R17" t="n">
-        <v>7022219</v>
+        <v>7022147</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128587761</v>
+        <v>128591182</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,13 +2495,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447673</v>
+        <v>447727</v>
       </c>
       <c r="R18" t="n">
-        <v>7022084</v>
+        <v>7022210</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128588406</v>
+        <v>128591273</v>
       </c>
       <c r="B19" t="n">
-        <v>83011</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,37 +2578,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447602</v>
+        <v>447733</v>
       </c>
       <c r="R19" t="n">
-        <v>7022100</v>
+        <v>7022244</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2637,7 +2652,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,10 +2679,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128586645</v>
+        <v>128854129</v>
       </c>
       <c r="B20" t="n">
-        <v>91526</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,24 +2708,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447644</v>
+        <v>447467</v>
       </c>
       <c r="R20" t="n">
-        <v>7022249</v>
+        <v>7022162</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2734,22 +2744,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,44 +2779,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128586291</v>
+        <v>128854957</v>
       </c>
       <c r="B21" t="n">
-        <v>83002</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2826,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447651</v>
+        <v>447477</v>
       </c>
       <c r="R21" t="n">
-        <v>7022237</v>
+        <v>7022152</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2841,22 +2856,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,22 +2891,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128591273</v>
+        <v>128856217</v>
       </c>
       <c r="B22" t="n">
-        <v>91526</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,24 +2932,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447733</v>
+        <v>447498</v>
       </c>
       <c r="R22" t="n">
-        <v>7022244</v>
+        <v>7022166</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2953,22 +2968,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,50 +3003,50 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128589408</v>
+        <v>128857160</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3035,13 +3055,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447502</v>
+        <v>447528</v>
       </c>
       <c r="R23" t="n">
-        <v>7022168</v>
+        <v>7022120</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3065,22 +3085,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,10 +3127,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128589039</v>
+        <v>128857221</v>
       </c>
       <c r="B24" t="n">
-        <v>91526</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,13 +3167,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447525</v>
+        <v>447579</v>
       </c>
       <c r="R24" t="n">
-        <v>7022147</v>
+        <v>7022145</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3177,22 +3197,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,57 +3239,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128591228</v>
+        <v>128854816</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>92369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447721</v>
+        <v>447483</v>
       </c>
       <c r="R25" t="n">
-        <v>7022210</v>
+        <v>7022158</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3293,22 +3304,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3323,44 +3339,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589765</v>
+        <v>128856170</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>92369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,13 +3386,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447553</v>
+        <v>447486</v>
       </c>
       <c r="R26" t="n">
-        <v>7022148</v>
+        <v>7022172</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3400,22 +3416,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På grov murken granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3430,60 +3451,69 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128586312</v>
+        <v>128586927</v>
       </c>
       <c r="B27" t="n">
-        <v>91526</v>
+        <v>79486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447610</v>
+        <v>447666</v>
       </c>
       <c r="R27" t="n">
-        <v>7022251</v>
+        <v>7022106</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,7 +3542,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3522,7 +3552,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3549,32 +3579,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128857156</v>
+        <v>128586050</v>
       </c>
       <c r="B28" t="n">
-        <v>91841</v>
+        <v>92281</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3584,13 +3614,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447528</v>
+        <v>447664</v>
       </c>
       <c r="R28" t="n">
-        <v>7022120</v>
+        <v>7022270</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3614,27 +3644,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,6 +3670,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3661,10 +3701,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128856217</v>
+        <v>128589328</v>
       </c>
       <c r="B29" t="n">
-        <v>91543</v>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,21 +3712,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,13 +3736,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447498</v>
+        <v>447558</v>
       </c>
       <c r="R29" t="n">
-        <v>7022166</v>
+        <v>7022168</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3726,27 +3766,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3761,22 +3801,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128859396</v>
+        <v>128857152</v>
       </c>
       <c r="B30" t="n">
-        <v>100899</v>
+        <v>96350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,21 +3824,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3808,13 +3848,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447545</v>
+        <v>447555</v>
       </c>
       <c r="R30" t="n">
-        <v>7022169</v>
+        <v>7022150</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3843,7 +3883,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3853,7 +3893,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig kalkgranskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,74 +3913,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128858970</v>
+        <v>128589559</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>92869</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447671</v>
+        <v>447547</v>
       </c>
       <c r="R31" t="n">
-        <v>7022102</v>
+        <v>7022212</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3959,27 +3990,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog, 36 plantor</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3994,44 +4020,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128854816</v>
+        <v>128592777</v>
       </c>
       <c r="B32" t="n">
-        <v>91996</v>
+        <v>92869</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4041,13 +4067,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447483</v>
+        <v>447658</v>
       </c>
       <c r="R32" t="n">
-        <v>7022158</v>
+        <v>7022305</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4071,27 +4097,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4106,44 +4127,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128854957</v>
+        <v>128859400</v>
       </c>
       <c r="B33" t="n">
-        <v>91543</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4153,13 +4174,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447477</v>
+        <v>447545</v>
       </c>
       <c r="R33" t="n">
-        <v>7022152</v>
+        <v>7022169</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4188,7 +4209,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4198,12 +4219,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,65 +4234,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128857221</v>
+        <v>128587720</v>
       </c>
       <c r="B34" t="n">
-        <v>91543</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447579</v>
+        <v>447673</v>
       </c>
       <c r="R34" t="n">
-        <v>7022145</v>
+        <v>7022084</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4300,22 +4311,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4342,10 +4353,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128859191</v>
+        <v>128588025</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,21 +4364,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4375,19 +4386,24 @@
           <t>40</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447654</v>
+        <v>447724</v>
       </c>
       <c r="R35" t="n">
-        <v>7022117</v>
+        <v>7022011</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4411,22 +4427,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4453,32 +4469,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128859166</v>
+        <v>128590184</v>
       </c>
       <c r="B36" t="n">
-        <v>82996</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4488,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447658</v>
+        <v>447613</v>
       </c>
       <c r="R36" t="n">
-        <v>7022103</v>
+        <v>7022111</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4518,27 +4534,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe i gammal granskog</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4553,44 +4564,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128854129</v>
+        <v>128856768</v>
       </c>
       <c r="B37" t="n">
-        <v>91543</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,13 +4611,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447467</v>
+        <v>447518</v>
       </c>
       <c r="R37" t="n">
-        <v>7022162</v>
+        <v>7022171</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4635,7 +4646,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4645,12 +4656,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4670,17 +4681,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128857410</v>
+        <v>128857488</v>
       </c>
       <c r="B38" t="n">
-        <v>98710</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,41 +4699,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447636</v>
+        <v>447669</v>
       </c>
       <c r="R38" t="n">
-        <v>7022220</v>
+        <v>7022248</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4751,7 +4758,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4761,7 +4768,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4776,12 +4788,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4791,11 +4803,11 @@
         <v>128859079</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4895,32 +4907,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128857152</v>
+        <v>128859089</v>
       </c>
       <c r="B40" t="n">
-        <v>95948</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4930,10 +4942,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447555</v>
+        <v>447640</v>
       </c>
       <c r="R40" t="n">
-        <v>7022150</v>
+        <v>7022114</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4965,7 +4977,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4975,12 +4987,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig kalkgranskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5010,11 +5022,11 @@
         <v>128859190</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5128,32 +5140,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128856170</v>
+        <v>128588406</v>
       </c>
       <c r="B42" t="n">
-        <v>91996</v>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5163,13 +5175,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447486</v>
+        <v>447602</v>
       </c>
       <c r="R42" t="n">
-        <v>7022172</v>
+        <v>7022100</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5193,27 +5205,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På grov murken granlåga i gammal granskog</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,22 +5235,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128859400</v>
+        <v>128588534</v>
       </c>
       <c r="B43" t="n">
-        <v>92498</v>
+        <v>80460</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5251,21 +5258,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5275,13 +5282,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447545</v>
+        <v>447602</v>
       </c>
       <c r="R43" t="n">
-        <v>7022169</v>
+        <v>7022100</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,22 +5312,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5340,39 +5347,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128857488</v>
+        <v>128857503</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>80460</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5382,10 +5389,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447669</v>
+        <v>447676</v>
       </c>
       <c r="R44" t="n">
-        <v>7022248</v>
+        <v>7022228</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5432,7 +5439,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5459,48 +5466,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128857090</v>
+        <v>128589408</v>
       </c>
       <c r="B45" t="n">
-        <v>91841</v>
+        <v>80467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447519</v>
+        <v>447502</v>
       </c>
       <c r="R45" t="n">
-        <v>7022129</v>
+        <v>7022168</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5524,22 +5536,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5566,10 +5578,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128859234</v>
+        <v>128589765</v>
       </c>
       <c r="B46" t="n">
-        <v>98710</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5594,34 +5606,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447586</v>
+        <v>447553</v>
       </c>
       <c r="R46" t="n">
-        <v>7022132</v>
+        <v>7022148</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5645,27 +5643,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På marken i fuktig granskog</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5680,60 +5673,69 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128859156</v>
+        <v>128591228</v>
       </c>
       <c r="B47" t="n">
-        <v>83003</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447663</v>
+        <v>447721</v>
       </c>
       <c r="R47" t="n">
-        <v>7022108</v>
+        <v>7022210</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5757,22 +5759,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5792,45 +5794,44 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128857160</v>
+        <v>128857410</v>
       </c>
       <c r="B48" t="n">
-        <v>91543</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5839,13 +5840,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447528</v>
+        <v>447636</v>
       </c>
       <c r="R48" t="n">
-        <v>7022120</v>
+        <v>7022220</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5874,7 +5875,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5884,7 +5885,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5904,44 +5905,44 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128859403</v>
+        <v>128857643</v>
       </c>
       <c r="B49" t="n">
-        <v>102176</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5949,21 +5950,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447541</v>
+        <v>447746</v>
       </c>
       <c r="R49" t="n">
-        <v>7022174</v>
+        <v>7022160</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5995,7 +5991,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,12 +6001,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På marken i rikare stråk i gammal kalkgranskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6037,45 +6033,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128856768</v>
+        <v>128857763</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447518</v>
+        <v>447780</v>
       </c>
       <c r="R50" t="n">
-        <v>7022171</v>
+        <v>7022116</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6107,7 +6112,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6117,12 +6122,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,52 +6147,66 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128855978</v>
+        <v>128858970</v>
       </c>
       <c r="B51" t="n">
-        <v>91841</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447481</v>
+        <v>447671</v>
       </c>
       <c r="R51" t="n">
-        <v>7022155</v>
+        <v>7022102</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6219,7 +6238,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6229,12 +6248,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog, 36 plantor</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,17 +6273,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128857643</v>
+        <v>128859191</v>
       </c>
       <c r="B52" t="n">
-        <v>98710</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6291,12 +6310,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6305,13 +6319,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447746</v>
+        <v>447654</v>
       </c>
       <c r="R52" t="n">
-        <v>7022160</v>
+        <v>7022117</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6340,7 +6354,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6350,12 +6364,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6370,57 +6379,71 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128857503</v>
+        <v>128859234</v>
       </c>
       <c r="B53" t="n">
-        <v>80176</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447676</v>
+        <v>447586</v>
       </c>
       <c r="R53" t="n">
-        <v>7022228</v>
+        <v>7022132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6452,7 +6475,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6462,12 +6485,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i fuktig granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6494,54 +6517,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128857763</v>
+        <v>128859390</v>
       </c>
       <c r="B54" t="n">
-        <v>98710</v>
+        <v>103682</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222002</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447780</v>
+        <v>447564</v>
       </c>
       <c r="R54" t="n">
-        <v>7022116</v>
+        <v>7022182</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6573,7 +6587,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6583,12 +6597,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6603,22 +6612,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128856585</v>
+        <v>128586443</v>
       </c>
       <c r="B55" t="n">
-        <v>80108</v>
+        <v>101326</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6626,21 +6635,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6650,10 +6659,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447500</v>
+        <v>447624</v>
       </c>
       <c r="R55" t="n">
-        <v>7022174</v>
+        <v>7022238</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6680,27 +6689,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På sälg i gammal granskog</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6715,44 +6719,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128859089</v>
+        <v>128859396</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>101325</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6762,13 +6766,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447640</v>
+        <v>447545</v>
       </c>
       <c r="R56" t="n">
-        <v>7022114</v>
+        <v>7022169</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6797,7 +6801,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6807,12 +6811,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6827,44 +6826,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128859390</v>
+        <v>128591149</v>
       </c>
       <c r="B57" t="n">
-        <v>103233</v>
+        <v>78339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222002</v>
+        <v>228579</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6874,13 +6873,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447564</v>
+        <v>447711</v>
       </c>
       <c r="R57" t="n">
-        <v>7022182</v>
+        <v>7022219</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6904,22 +6903,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6939,58 +6938,55 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128857255</v>
+        <v>128856585</v>
       </c>
       <c r="B58" t="n">
-        <v>91941</v>
+        <v>80392</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>E14  mellan Trångsviken och Mattmar, E14  mellan Trångsviken och Mattmar, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447578</v>
+        <v>447500</v>
       </c>
       <c r="R58" t="n">
-        <v>7022145</v>
+        <v>7022174</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7019,7 +7015,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7029,28 +7025,32 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 40318-2025 artfynd.xlsx
+++ b/artfynd/A 40318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857255</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859166</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859156</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586291</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587013</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586567</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128855978</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857090</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857156</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586312</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586544</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2116,6 +2181,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586645</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2228,6 +2298,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586845</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2340,6 +2415,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587761</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,6 +2532,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589039</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2564,6 +2649,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128591182</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2676,6 +2766,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128591273</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2788,6 +2883,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128854129</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2900,6 +3000,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128854957</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3012,6 +3117,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128856217</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3124,6 +3234,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857160</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3236,6 +3351,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857221</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3348,6 +3468,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128854816</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3460,6 +3585,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128856170</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3576,6 +3706,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586927</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3698,6 +3833,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586050</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3810,6 +3950,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589328</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3922,6 +4067,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857152</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4029,6 +4179,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589559</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4136,6 +4291,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128592777</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4243,6 +4403,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859400</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4350,6 +4515,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587720</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4466,6 +4636,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4573,6 +4748,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128590184</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4685,6 +4865,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128856768</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4797,6 +4982,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857488</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4904,6 +5094,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859079</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5016,6 +5211,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859089</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5137,6 +5337,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859190</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5244,6 +5449,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588406</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5351,6 +5561,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588534</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5463,6 +5678,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857503</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5575,6 +5795,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589408</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5682,6 +5907,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128589765</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5798,6 +6028,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128591228</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5909,6 +6144,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857410</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6030,6 +6270,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857643</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6151,6 +6396,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128857763</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6277,6 +6527,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128858970</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6388,6 +6643,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859191</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6514,6 +6774,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859234</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6621,6 +6886,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859390</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6728,6 +6998,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128586443</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6835,6 +7110,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128859396</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6942,6 +7222,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128591149</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7054,8 +7339,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128856585</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>